--- a/data/interim/exposure_coding.xlsx
+++ b/data/interim/exposure_coding.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="600" windowWidth="34400" windowHeight="28200" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="coding" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="source_register" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="source_to_waves" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="coding" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="source_register" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="source_to_waves" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>

--- a/data/interim/exposure_coding.xlsx
+++ b/data/interim/exposure_coding.xlsx
@@ -10,15 +10,18 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="source_register" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="source_to_waves" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="source_register" localSheetId="1">source_register!$A$1:$K$32</definedName>
+  </definedNames>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,95 +54,16 @@
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="23">
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="yyyy/mm/dd"/>
-      <alignment horizontal="center" vertical="bottom"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="yyyy/mm/dd"/>
-      <alignment horizontal="center" vertical="bottom"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom"/>
-    </dxf>
-  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -210,25 +134,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table3" displayName="Table3" ref="A1:I1048576" headerRowCount="1" totalsRowShown="0">
-  <autoFilter ref="A1:I1048576"/>
-  <tableColumns count="10">
-    <tableColumn id="1" name="source_id"/>
-    <tableColumn id="2" name="full_citation"/>
-    <tableColumn id="3" name="type"/>
-    <tableColumn id="4" name="published"/>
-    <tableColumn id="5" name="activity_start"/>
-    <tableColumn id="10" name="activity_end"/>
-    <tableColumn id="11" name="countries"/>
-    <tableColumn id="6" name="independence"/>
-    <tableColumn id="7" name="local_path"/>
-    <tableColumn id="8" name="Column2"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12098,64 +12003,1662 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col width="15.83203125" customWidth="1" style="3" min="1" max="9"/>
+    <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="80.6640625" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="41.6640625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="19.5" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="10.1640625" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="11.1640625" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="10.5" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="80.6640625" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col width="11.83203125" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="19.6640625" bestFit="1" customWidth="1" min="10" max="10"/>
+    <col width="80.6640625" bestFit="1" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>source_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>full_citation</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>author</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>published</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>activity_start</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>activity_end</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>countries</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>independence</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>local_path</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>online_url</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>EDL22</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Doppelganger: Media clones serving Russian Propaganda</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>EU DisinfoLab</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>NGO / Research</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>44831</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>44682</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>44805</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>DE ABC; IT ABC; FR ABC; LV ABC; LT AB; EE AB</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>sources/EDL22.pdf</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.disinfo.eu/doppelganger</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>DFR22</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Russia-based Facebook operation targeted Europe with anti-Ukraine messaging</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>DFRLab</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>NGO / Research</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>44831</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>44621</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>44774</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>DE ABC; FR ABC; IT ABC; LV ABC; PL AC</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>sources/DFR22.pdf</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>https://dfrlab.org/2022/09/27/russia-based-facebook-operation-targeted-europe-with-anti-ukraine-messaging/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>MET22</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Removing Coordinated Inauthentic Behavior From China and Russia</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Platform Disclosure</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>44831</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>44682</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>44896</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>DE ABC; FR ABC; IT ABC; LV AB</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>sources/MET22.pdf</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>https://about.fb.com/news/2022/09/removing-coordinated-inauthentic-behavior-from-china-and-russia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>ISD22</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Pro-Kremlin network impersonates legitimate websites and floods social media with lies</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Institute for Strategic Dialogue</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>NGO / Research</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>44713</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>44796</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>DE ABC; FR ABC; IT ABC</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>sources/ISD22.pdf</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.isdglobal.org/digital-dispatch/pro-kremlin-network-impersonates-legitimate-websites-and-floods-social-media-with-lies/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>VIG23</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>RRN: A complex and persistent information manipulation campaign ‚Äì¬†technical report</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>VIGINUM</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>State Forensic</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>45126</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>44958</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>45078</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>FR ABC; DE ABC</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>sources/VIG23.pdf</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sgdsn.gouv.fr/publications/maj-19062023-rrn-une-campagne-numerique-de-manipulation-de-linformation-complexe-et</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>RST23</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Under the Radar: Vast Networks of Fake Accounts Raise Questions About Meta‚Äôs Compliance with the EU‚Äôs New Digital Rulebook.</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Reset Tech</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>NGO / Research</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>45139</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>44927</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>45017</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>DE ABC; FR ABC; IT C</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>sources/RST23.pdf</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reset.tech/resources/vast-networks-of-fake-accounts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>MET23</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Adversarial Threat Report, Second Quarter</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Platform Disclosure</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>45139</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>45017</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>45078</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>DE ABC; FR ABC; PL ABC</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>sources/MET23.pdf</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>https://transparency.meta.com/sr/Q2-2023-Adversarial-threat-report/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>VIG24</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Portal Kombat: A structured and coordinated pro-Russian propaganda network</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>VIGINUM</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>State Forensic</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>45334</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>45170</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>45261</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>DE ABC; FR ABC; AT ABC; PL ABC; ES ABC</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>sources/VIG24.pdf</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sgdsn.gouv.fr/files/files/20240212_NP_SGDSN_VIGINUM_PORTAL-KOMBAT-NETWORK_ENG_VF.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>AIF24</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>No Embargo in Sight: Meta lets Pro-Russia Propaganda Ads Flood the EU</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>AI Forensics</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>NGO / Research</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>45399</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>45155</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>45382</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>DE AC; FR AC</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>sources/AIF24.pdf</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>https://aiforensics.org/work/meta-political-ads</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>AIF24-2</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Supporting Evidence: Pro-Russian Ads Campaigns Approved by Meta from May 1 to May 27, 2024 in Italy, Germany, France &amp; Poland</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>AI Forensics</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>NGO / Research</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>45439</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>45413</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>45439</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>DE: AC; FR AC; IT AC; PL AC</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>sources/AIF24-2.pdf</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>https://cmsbackend.aiforensics.org/uploads/Meta_Ads_Follow_up_27_May_24_46d87a3953.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>SEK24</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Master of Puppets: Uncovering the DoppelG√§nger pro-Russian influence campaign</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Sekoia</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Threat Intel</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>45433</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>45231</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>45383</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>FR ABC; DE ABC; LT A; IT AC; SK A</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>sources/SEK24.pdf</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sekoia.com/blog/master-of-puppets-uncovering-the-doppelganger-pro-russian-influence-campaign#toc-3-i-doppelgnger-campaign-victims-objective</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>MET24</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Adversarial Threat Report, Second Quarter</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Platform Disclosure</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>45505</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>45383</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>45444</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>DE AC; FR AC; PL AC</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>sources/MET24.pdf</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>https://transparency.meta.com/sr/Q2-2024-Adversarial-threat-report/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>OAI24</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>AI and Covert Influence Operations: Latest Trends</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Platform Disclosure</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>45323</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>45383</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>DE AC; FR AC; PL AC; IT AC</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>sources/OAI24.pdf</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>https://openai.com/index/disrupting-deceptive-uses-of-ai-by-covert-influence-operations/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>EDM24</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Russian disinformation network ‚ÄúPravda‚Äù grew bigger in the EU, even after its uncovering</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>European Digital Media Observatory</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>NGO / Research</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>45406</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>45352</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>45383</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>EL AC; IT AC; NL AC; DK AC; HR AC; CZ AC; SK AC; BG AC; RO AC; FI AC; SE AC; PT AC; EE AC; LV AC; LT AC; HU AC; CY AC; IE AC; SI AC</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>sources/EDM24.pdf</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>https://edmo.eu/publications/russian-disinformation-network-pravda-grew-bigger-in-the-eu-even-after-its-uncovering/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>CHK24</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Operation Overload: how pro-Russian actors flood newsrooms with fake content and seek to divert their efforts</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>CheckFirst</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Threat Intel</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>45447</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>45139</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>45383</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>DE ABC; FR ABC</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>sources/CHK24.pdf</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>https://checkfirst.network/operation-overload-how-pro-russian-actors-flood-newsrooms-with-fake-content-and-seek-to-divert-their-efforts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>VIG24-2</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Matryoshka: A pro-Russian campaign targeting media and the fact-checking community</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>VIGINUM</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>State Forensic</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>45454</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>45174</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>45444</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>FR ABC; DE AC; IT AC</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>sources/VIG24-2.pdf</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sgdsn.gouv.fr/files/files/20240611_NP_SGDSN_VIGINUM_Matriochka_EN_VF.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>FFO24</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Germany Targeted by the Pro-Russian Disinformation Campaign ‚ÄúDoppelg√§nger‚Äù</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>German Federal Foreign Office</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>State Forensic</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>45448</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>44986</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>45437</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>DE ABC</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>sources/FFO24.pdf</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.auswaertiges-amt.de/resource/blob/2682484/2da31936d1cbeb9faec49df74d8bbe2e/technischer-bericht-desinformationskampagne-doppelgaenger-1--data.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>EAS24</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Doppelganger strikes back: FIMI activities in the context of the EE24</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>European External Action Service</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>State Forensic</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>45462</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>45444</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>DE ABC; FR ABC; IT ABC; PL ABC; ES ABC</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>sources/EAS24.pdf</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>https://euvsdisinfo.eu/uploads/2024/06/EEAS-TechnicalReport-DoppelgangerEE24_June2024.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>DFR24</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Doppelganger targets Ukrainian and French audiences via Facebook ads</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>DFRLab</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>NGO / Research</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>45363</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>45108</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>45323</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>FR ABC; DE ABC</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>sources/DFR24.pdf</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>https://dfrlab.org/2024/03/12/doppelganger-operation-targets-ukraine/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>HFL24</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Mid-year Doppelganger Information Operations in Europe and the US</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>HarfangLab</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Threat Intel</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>45413</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>45474</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>FR ABC; DE ABC; PL AC; HU A</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>sources/HFL24.pdf</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>https://harfanglab.io/insidethelab/doppelganger-operations-europe-us/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>BLV24-ENG</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Internal Details on the Russian Disinformation Campaign "Doppelg√§nger"</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Bavarian Office for the Protection of the Constitution</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>State Forensic</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>45505</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>45047</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>45474</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>DE ABC; FR ABC; PL AC; IT AC; ES AC</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>sources/BLV24-ENG.pdf</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lfv.bayern.de/wp-content/uploads/2025/05/baylfv_vollanalyse_doppelgaenger.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>SNT24</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Doppelg√§nger | Russia-Aligned Influence Operation Targets Germany </t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Sentinel Labs</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Threat Intel</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>45344</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>45231</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>45323</v>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>DE ABC</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>sources/SNT24.pdf</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sentinelone.com/labs/doppelganger-russia-aligned-influence-operation-targets-germany/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>REC23</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Obfuscation and AI Content in the Russian Influence Network ‚ÄúDoppelg√§nger‚Äù Signals Evolving Tactics</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Recorded Future</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Threat Intel</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>45265</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>45231</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>45231</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>DE ABC</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>sources/REC23.pdf</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.recordedfuture.com/research/russian-influence-network-doppelgangers-ai-content-tactics</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>SKY24</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Doppelg√§nger NG | Russian Cyberwarfare campaign</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>ClearSky Cyber Security</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Threat Intel</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>45344</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>45292</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>45323</v>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>DE ABC; FR ABC</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>sources/SKY24.pdf</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.clearskysec.com/dg/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>ISD25</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Coordinated disinformation network uses AI, media impersonation to target German election</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Institute for Strategic Dialogue</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>NGO / Research</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>45701</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>45597</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>DE AB</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>sources/ISD25.pdf</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.isdglobal.org/digital-dispatch/coordinated-disinformation-network-uses-ai-media-impersonation-to-target-german-election/</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>REC25</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Stimmen aus Moskau: Russian Influence Operations Target German Elections</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Recorded Future</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Threat Intel</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>45701</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>45566</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>45689</v>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>DE ABC</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>sources/REC25.pdf</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.recordedfuture.com/research/stimmen-aus-moskau-russian-influence-operations-target-german-elections</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>CMS24</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>To be continued: The pro-Kremlin disinformation campaign Doppelganger in Germany</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>CeMAS</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>NGO / Research</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>45615</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>45231</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>45566</v>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>DE ABC; FR AC; IT AC; PL AC</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>sources/CMS24.pdf</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>https://cemas.io/en/publications/to-be-continued-doppelganger-germany</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>CMS25-ENG</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Russische Desinformation vor der Bundestagswahl: Doppelg√§nger-Kampagne macht Stimmung gegen Parteien</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>CeMAS</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>NGO / Research</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>45677</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>45643</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>45671</v>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>DE ABC</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>sources/CMS25-ENG.pdf</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>https://btw2025.cemas.io/artikel/update-doppelgaenger</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>CHK25</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Influence by Design: Doppelg√§nger Sanctions, Meta and the Social Design Agency</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>CheckFirst</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Threat Intel</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>45658</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>44682</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>45566</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>FR AC; DE AC; IT AC; PL AC</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>sources/CHK25.pdf</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>https://checkfirst.network/wp-content/uploads/2025/01/Influence_by_Design.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>MET25</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Adversarial Threat Report, Fourth Quarter</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Platform Disclosure</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>45689</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>45566</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>45627</v>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>FR A; DE A; PL A</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>sources/MET25.pdf</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>https://transparency.meta.com/sr/Q4-2024-Adversarial-threat-report/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>MET24-2</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Q2_2023_Doppelganger_Russia_based_CIB_network_updated.csv</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Platform Disclosure</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>45629</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>44713</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>45597</v>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>FR AB; DE AB; IT AB; LV AB; PL AB</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>sources/MET24-2.csv</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/facebook/threat-research/blob/main/indicators/csv/Q2_2023%20/Q2_2023_Doppelganger_Russia_based_CIB_network_updated.csv</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 

--- a/data/interim/exposure_coding.xlsx
+++ b/data/interim/exposure_coding.xlsx
@@ -19,11 +19,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
     <numFmt numFmtId="166" formatCode="YYYY-MM-DD"/>
-    <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -570,17 +569,6 @@
       <c r="H2" t="n">
         <v>0</v>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
       <c r="T2" t="n">
         <v>0</v>
       </c>
@@ -619,17 +607,6 @@
       <c r="H3" t="n">
         <v>0</v>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
       <c r="T3" t="n">
         <v>0</v>
       </c>
@@ -668,17 +645,6 @@
       <c r="H4" t="n">
         <v>0</v>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
       <c r="T4" t="n">
         <v>0</v>
       </c>
@@ -717,17 +683,6 @@
       <c r="H5" t="n">
         <v>0</v>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
       <c r="T5" t="n">
         <v>0</v>
       </c>
@@ -776,22 +731,16 @@
           <t>CHK25</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>DFR22</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>EDL22</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>A:CHK25,DFR22,EDL22,ISD22,MET22,MET24-2 | B:DFR22,EDL22,ISD22,MET22,MET24-2 | C:CHK25,DFR22,EDL22,ISD22,MET22</t>
@@ -845,14 +794,6 @@
           <t>EDL22</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>A:EDL22 | B:EDL22</t>
@@ -896,17 +837,6 @@
       <c r="H8" t="n">
         <v>0</v>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
       <c r="T8" t="n">
         <v>0</v>
       </c>
@@ -945,17 +875,6 @@
       <c r="H9" t="n">
         <v>0</v>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
       <c r="T9" t="n">
         <v>0</v>
       </c>
@@ -994,17 +913,6 @@
       <c r="H10" t="n">
         <v>0</v>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
       <c r="T10" t="n">
         <v>0</v>
       </c>
@@ -1053,22 +961,16 @@
           <t>CHK25</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
           <t>DFR22</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>EDL22</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>A:CHK25,DFR22,EDL22,ISD22,MET22,MET24-2 | B:DFR22,EDL22,ISD22,MET22,MET24-2 | C:CHK25,DFR22,EDL22,ISD22,MET22</t>
@@ -1112,17 +1014,6 @@
       <c r="H12" t="n">
         <v>0</v>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
       <c r="T12" t="n">
         <v>0</v>
       </c>
@@ -1171,22 +1062,16 @@
           <t>CHK25</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
           <t>DFR22</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>EDL22</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>A:CHK25,DFR22,EDL22,ISD22,MET22,MET24-2 | B:DFR22,EDL22,ISD22,MET22,MET24-2 | C:CHK25,DFR22,EDL22,ISD22,MET22</t>
@@ -1230,17 +1115,6 @@
       <c r="H14" t="n">
         <v>0</v>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
       <c r="T14" t="n">
         <v>0</v>
       </c>
@@ -1289,22 +1163,16 @@
           <t>DFR22</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
           <t>EDL22</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>MET22</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>A:DFR22,EDL22,MET22,MET24-2 | B:DFR22,EDL22,MET22,MET24-2 | C:DFR22,EDL22</t>
@@ -1358,14 +1226,6 @@
           <t>EDL22</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>A:EDL22 | B:EDL22</t>
@@ -1409,17 +1269,6 @@
       <c r="H17" t="n">
         <v>0</v>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
       <c r="T17" t="n">
         <v>0</v>
       </c>
@@ -1458,17 +1307,6 @@
       <c r="H18" t="n">
         <v>0</v>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
       <c r="T18" t="n">
         <v>0</v>
       </c>
@@ -1507,17 +1345,6 @@
       <c r="H19" t="n">
         <v>0</v>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
       <c r="T19" t="n">
         <v>0</v>
       </c>
@@ -1556,17 +1383,6 @@
       <c r="H20" t="n">
         <v>0</v>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
       <c r="T20" t="n">
         <v>0</v>
       </c>
@@ -1605,17 +1421,6 @@
       <c r="H21" t="n">
         <v>0</v>
       </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
       <c r="T21" t="n">
         <v>0</v>
       </c>
@@ -1664,22 +1469,16 @@
           <t>CHK25</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
           <t>DFR22</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>MET24-2</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>A:CHK25,DFR22,MET24-2 | B:MET24-2 | C:CHK25,DFR22</t>
@@ -1723,17 +1522,6 @@
       <c r="H23" t="n">
         <v>0</v>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
       <c r="T23" t="n">
         <v>0</v>
       </c>
@@ -1772,17 +1560,6 @@
       <c r="H24" t="n">
         <v>0</v>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
       <c r="T24" t="n">
         <v>0</v>
       </c>
@@ -1821,17 +1598,6 @@
       <c r="H25" t="n">
         <v>0</v>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
       <c r="T25" t="n">
         <v>0</v>
       </c>
@@ -1870,17 +1636,6 @@
       <c r="H26" t="n">
         <v>0</v>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
       <c r="T26" t="n">
         <v>0</v>
       </c>
@@ -1919,17 +1674,6 @@
       <c r="H27" t="n">
         <v>0</v>
       </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
       <c r="T27" t="n">
         <v>0</v>
       </c>
@@ -1968,17 +1712,6 @@
       <c r="H28" t="n">
         <v>0</v>
       </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
       <c r="T28" t="n">
         <v>0</v>
       </c>
@@ -2017,17 +1750,6 @@
       <c r="H29" t="n">
         <v>0</v>
       </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
       <c r="T29" t="n">
         <v>0</v>
       </c>
@@ -2066,17 +1788,6 @@
       <c r="H30" t="n">
         <v>0</v>
       </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
       <c r="T30" t="n">
         <v>0</v>
       </c>
@@ -2115,17 +1826,6 @@
       <c r="H31" t="n">
         <v>0</v>
       </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
       <c r="T31" t="n">
         <v>0</v>
       </c>
@@ -2164,17 +1864,6 @@
       <c r="H32" t="n">
         <v>0</v>
       </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
       <c r="T32" t="n">
         <v>0</v>
       </c>
@@ -2223,22 +1912,16 @@
           <t>CHK25</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
           <t>DFR22</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
           <t>EDL22</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr">
         <is>
           <t>A:CHK25,DFR22,EDL22,ISD22,MET22,MET24-2,RST23,VIG23 | B:DFR22,EDL22,ISD22,MET22,MET24-2,RST23,VIG23 | C:CHK25,DFR22,EDL22,ISD22,MET22,RST23,VIG23</t>
@@ -2292,14 +1975,6 @@
           <t>EDL22</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr">
         <is>
           <t>A:EDL22 | B:EDL22</t>
@@ -2343,17 +2018,6 @@
       <c r="H35" t="n">
         <v>0</v>
       </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
       <c r="T35" t="n">
         <v>0</v>
       </c>
@@ -2392,17 +2056,6 @@
       <c r="H36" t="n">
         <v>0</v>
       </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
       <c r="T36" t="n">
         <v>0</v>
       </c>
@@ -2441,17 +2094,6 @@
       <c r="H37" t="n">
         <v>0</v>
       </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
       <c r="T37" t="n">
         <v>0</v>
       </c>
@@ -2500,22 +2142,16 @@
           <t>CHK25</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
           <t>DFR22</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
           <t>EDL22</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr">
         <is>
           <t>A:CHK25,DFR22,EDL22,ISD22,MET22,MET24-2,RST23,VIG23 | B:DFR22,EDL22,ISD22,MET22,MET24-2,RST23,VIG23 | C:CHK25,DFR22,EDL22,ISD22,MET22,RST23,VIG23</t>
@@ -2559,17 +2195,6 @@
       <c r="H39" t="n">
         <v>0</v>
       </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
       <c r="T39" t="n">
         <v>0</v>
       </c>
@@ -2618,22 +2243,16 @@
           <t>CHK25</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
           <t>DFR22</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
           <t>EDL22</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr">
         <is>
           <t>A:CHK25,DFR22,EDL22,ISD22,MET22,MET24-2 | B:DFR22,EDL22,ISD22,MET22,MET24-2 | C:CHK25,DFR22,EDL22,ISD22,MET22,RST23</t>
@@ -2677,17 +2296,6 @@
       <c r="H41" t="n">
         <v>0</v>
       </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
       <c r="T41" t="n">
         <v>0</v>
       </c>
@@ -2736,22 +2344,16 @@
           <t>DFR22</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
           <t>EDL22</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
           <t>MET22</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr">
         <is>
           <t>A:DFR22,EDL22,MET22,MET24-2 | B:DFR22,EDL22,MET22,MET24-2 | C:DFR22,EDL22</t>
@@ -2805,14 +2407,6 @@
           <t>EDL22</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr">
         <is>
           <t>A:EDL22 | B:EDL22</t>
@@ -2856,17 +2450,6 @@
       <c r="H44" t="n">
         <v>0</v>
       </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
       <c r="T44" t="n">
         <v>0</v>
       </c>
@@ -2905,17 +2488,6 @@
       <c r="H45" t="n">
         <v>0</v>
       </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
-      <c r="S45" t="inlineStr"/>
       <c r="T45" t="n">
         <v>0</v>
       </c>
@@ -2954,17 +2526,6 @@
       <c r="H46" t="n">
         <v>0</v>
       </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
       <c r="T46" t="n">
         <v>0</v>
       </c>
@@ -3003,17 +2564,6 @@
       <c r="H47" t="n">
         <v>0</v>
       </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
-      <c r="S47" t="inlineStr"/>
       <c r="T47" t="n">
         <v>0</v>
       </c>
@@ -3052,17 +2602,6 @@
       <c r="H48" t="n">
         <v>0</v>
       </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr"/>
-      <c r="S48" t="inlineStr"/>
       <c r="T48" t="n">
         <v>0</v>
       </c>
@@ -3111,22 +2650,16 @@
           <t>CHK25</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
           <t>DFR22</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
           <t>MET24-2</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr">
         <is>
           <t>A:CHK25,DFR22,MET24-2 | B:MET24-2 | C:CHK25,DFR22</t>
@@ -3170,17 +2703,6 @@
       <c r="H50" t="n">
         <v>0</v>
       </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr"/>
       <c r="T50" t="n">
         <v>0</v>
       </c>
@@ -3219,17 +2741,6 @@
       <c r="H51" t="n">
         <v>0</v>
       </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="inlineStr"/>
       <c r="T51" t="n">
         <v>0</v>
       </c>
@@ -3268,17 +2779,6 @@
       <c r="H52" t="n">
         <v>0</v>
       </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr"/>
-      <c r="S52" t="inlineStr"/>
       <c r="T52" t="n">
         <v>0</v>
       </c>
@@ -3317,17 +2817,6 @@
       <c r="H53" t="n">
         <v>0</v>
       </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="inlineStr"/>
       <c r="T53" t="n">
         <v>0</v>
       </c>
@@ -3366,17 +2855,6 @@
       <c r="H54" t="n">
         <v>0</v>
       </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr"/>
       <c r="T54" t="n">
         <v>0</v>
       </c>
@@ -3415,17 +2893,6 @@
       <c r="H55" t="n">
         <v>0</v>
       </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="inlineStr"/>
       <c r="T55" t="n">
         <v>0</v>
       </c>
@@ -3464,17 +2931,6 @@
       <c r="H56" t="n">
         <v>0</v>
       </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
-      <c r="S56" t="inlineStr"/>
       <c r="T56" t="n">
         <v>0</v>
       </c>
@@ -3513,17 +2969,6 @@
       <c r="H57" t="n">
         <v>0</v>
       </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="inlineStr"/>
       <c r="T57" t="n">
         <v>0</v>
       </c>
@@ -3562,17 +3007,6 @@
       <c r="H58" t="n">
         <v>0</v>
       </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr"/>
-      <c r="S58" t="inlineStr"/>
       <c r="T58" t="n">
         <v>0</v>
       </c>
@@ -3611,17 +3045,6 @@
       <c r="H59" t="n">
         <v>0</v>
       </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr"/>
-      <c r="S59" t="inlineStr"/>
       <c r="T59" t="n">
         <v>0</v>
       </c>
@@ -3670,22 +3093,16 @@
           <t>BLV24-ENG</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
           <t>CHK25</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
           <t>EAS24</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr">
         <is>
           <t>A:BLV24-ENG,CHK25,EAS24,FFO24,MET23,MET24-2,RST23,VIG23 | B:BLV24-ENG,EAS24,FFO24,MET23,MET24-2,RST23,VIG23 | C:BLV24-ENG,CHK25,EAS24,FFO24,MET23,RST23,VIG23</t>
@@ -3729,17 +3146,6 @@
       <c r="H61" t="n">
         <v>0</v>
       </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
-      <c r="S61" t="inlineStr"/>
       <c r="T61" t="n">
         <v>0</v>
       </c>
@@ -3778,17 +3184,6 @@
       <c r="H62" t="n">
         <v>0</v>
       </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr"/>
-      <c r="S62" t="inlineStr"/>
       <c r="T62" t="n">
         <v>0</v>
       </c>
@@ -3827,17 +3222,6 @@
       <c r="H63" t="n">
         <v>0</v>
       </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr"/>
-      <c r="S63" t="inlineStr"/>
       <c r="T63" t="n">
         <v>0</v>
       </c>
@@ -3886,18 +3270,11 @@
           <t>BLV24-ENG</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
           <t>EAS24</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr">
         <is>
           <t>A:BLV24-ENG,EAS24 | B:EAS24 | C:BLV24-ENG,EAS24</t>
@@ -3951,22 +3328,16 @@
           <t>BLV24-ENG</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
           <t>CHK25</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
           <t>EAS24</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr">
         <is>
           <t>A:BLV24-ENG,CHK25,EAS24,MET23,MET24-2,RST23,VIG23 | B:BLV24-ENG,EAS24,MET23,MET24-2,RST23,VIG23 | C:BLV24-ENG,CHK25,EAS24,MET23,RST23,VIG23</t>
@@ -4010,17 +3381,6 @@
       <c r="H66" t="n">
         <v>0</v>
       </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="inlineStr"/>
-      <c r="S66" t="inlineStr"/>
       <c r="T66" t="n">
         <v>0</v>
       </c>
@@ -4069,22 +3429,16 @@
           <t>BLV24-ENG</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
           <t>CHK25</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
           <t>EAS24</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr">
         <is>
           <t>A:BLV24-ENG,CHK25,EAS24,MET24-2 | B:EAS24,MET24-2 | C:BLV24-ENG,CHK25,EAS24,RST23</t>
@@ -4128,17 +3482,6 @@
       <c r="H68" t="n">
         <v>0</v>
       </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="inlineStr"/>
-      <c r="S68" t="inlineStr"/>
       <c r="T68" t="n">
         <v>0</v>
       </c>
@@ -4187,14 +3530,6 @@
           <t>MET24-2</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="inlineStr"/>
       <c r="S69" t="inlineStr">
         <is>
           <t>A:MET24-2 | B:MET24-2</t>
@@ -4238,17 +3573,6 @@
       <c r="H70" t="n">
         <v>0</v>
       </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="inlineStr"/>
-      <c r="S70" t="inlineStr"/>
       <c r="T70" t="n">
         <v>0</v>
       </c>
@@ -4287,17 +3611,6 @@
       <c r="H71" t="n">
         <v>0</v>
       </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr"/>
-      <c r="Q71" t="inlineStr"/>
-      <c r="R71" t="inlineStr"/>
-      <c r="S71" t="inlineStr"/>
       <c r="T71" t="n">
         <v>0</v>
       </c>
@@ -4336,17 +3649,6 @@
       <c r="H72" t="n">
         <v>0</v>
       </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="inlineStr"/>
-      <c r="R72" t="inlineStr"/>
-      <c r="S72" t="inlineStr"/>
       <c r="T72" t="n">
         <v>0</v>
       </c>
@@ -4385,17 +3687,6 @@
       <c r="H73" t="n">
         <v>0</v>
       </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr"/>
-      <c r="R73" t="inlineStr"/>
-      <c r="S73" t="inlineStr"/>
       <c r="T73" t="n">
         <v>0</v>
       </c>
@@ -4434,17 +3725,6 @@
       <c r="H74" t="n">
         <v>0</v>
       </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="inlineStr"/>
-      <c r="S74" t="inlineStr"/>
       <c r="T74" t="n">
         <v>0</v>
       </c>
@@ -4483,17 +3763,6 @@
       <c r="H75" t="n">
         <v>0</v>
       </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr"/>
-      <c r="R75" t="inlineStr"/>
-      <c r="S75" t="inlineStr"/>
       <c r="T75" t="n">
         <v>0</v>
       </c>
@@ -4542,22 +3811,16 @@
           <t>BLV24-ENG</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
           <t>CHK25</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
           <t>EAS24</t>
         </is>
       </c>
-      <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr"/>
-      <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr">
         <is>
           <t>A:BLV24-ENG,CHK25,EAS24,MET23,MET24-2 | B:EAS24,MET23,MET24-2 | C:BLV24-ENG,CHK25,EAS24,MET23</t>
@@ -4601,17 +3864,6 @@
       <c r="H77" t="n">
         <v>0</v>
       </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr"/>
-      <c r="R77" t="inlineStr"/>
-      <c r="S77" t="inlineStr"/>
       <c r="T77" t="n">
         <v>0</v>
       </c>
@@ -4650,17 +3902,6 @@
       <c r="H78" t="n">
         <v>0</v>
       </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
-      <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr"/>
-      <c r="R78" t="inlineStr"/>
-      <c r="S78" t="inlineStr"/>
       <c r="T78" t="n">
         <v>0</v>
       </c>
@@ -4699,17 +3940,6 @@
       <c r="H79" t="n">
         <v>0</v>
       </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="inlineStr"/>
-      <c r="R79" t="inlineStr"/>
-      <c r="S79" t="inlineStr"/>
       <c r="T79" t="n">
         <v>0</v>
       </c>
@@ -4748,17 +3978,6 @@
       <c r="H80" t="n">
         <v>0</v>
       </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr"/>
-      <c r="R80" t="inlineStr"/>
-      <c r="S80" t="inlineStr"/>
       <c r="T80" t="n">
         <v>0</v>
       </c>
@@ -4797,17 +4016,6 @@
       <c r="H81" t="n">
         <v>0</v>
       </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
-      <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr"/>
-      <c r="R81" t="inlineStr"/>
-      <c r="S81" t="inlineStr"/>
       <c r="T81" t="n">
         <v>0</v>
       </c>
@@ -4846,17 +4054,6 @@
       <c r="H82" t="n">
         <v>0</v>
       </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr"/>
-      <c r="R82" t="inlineStr"/>
-      <c r="S82" t="inlineStr"/>
       <c r="T82" t="n">
         <v>0</v>
       </c>
@@ -4895,17 +4092,6 @@
       <c r="H83" t="n">
         <v>0</v>
       </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
-      <c r="O83" t="inlineStr"/>
-      <c r="P83" t="inlineStr"/>
-      <c r="Q83" t="inlineStr"/>
-      <c r="R83" t="inlineStr"/>
-      <c r="S83" t="inlineStr"/>
       <c r="T83" t="n">
         <v>0</v>
       </c>
@@ -4944,17 +4130,6 @@
       <c r="H84" t="n">
         <v>0</v>
       </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
-      <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="inlineStr"/>
-      <c r="R84" t="inlineStr"/>
-      <c r="S84" t="inlineStr"/>
       <c r="T84" t="n">
         <v>0</v>
       </c>
@@ -4993,17 +4168,6 @@
       <c r="H85" t="n">
         <v>0</v>
       </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr"/>
-      <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr"/>
-      <c r="R85" t="inlineStr"/>
-      <c r="S85" t="inlineStr"/>
       <c r="T85" t="n">
         <v>0</v>
       </c>
@@ -5042,17 +4206,6 @@
       <c r="H86" t="n">
         <v>0</v>
       </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
-      <c r="O86" t="inlineStr"/>
-      <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="inlineStr"/>
-      <c r="R86" t="inlineStr"/>
-      <c r="S86" t="inlineStr"/>
       <c r="T86" t="n">
         <v>0</v>
       </c>
@@ -5101,32 +4254,26 @@
           <t>AIF24</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr">
         <is>
           <t>BLV24-ENG</t>
         </is>
       </c>
-      <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr">
         <is>
-          <t>CHK24</t>
-        </is>
-      </c>
-      <c r="O87" t="inlineStr"/>
-      <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr"/>
-      <c r="R87" t="inlineStr"/>
+          <t>CHK25</t>
+        </is>
+      </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>A:AIF24,BLV24-ENG,CHK24,CHK25,CMS24,DFR24,EAS24,FFO24,MET23,MET24-2,SNT24,VIG23,VIG24,VIG24-2 | B:BLV24-ENG,CHK24,CMS24,DFR24,EAS24,FFO24,MET23,MET24-2,SNT24,VIG23,VIG24 | C:AIF24,BLV24-ENG,CHK24,CHK25,CMS24,DFR24,EAS24,FFO24,MET23,SNT24,VIG23,VIG24,VIG24-2</t>
+          <t>A:AIF24,BLV24-ENG,CHK25,CMS24,DFR24,EAS24,FFO24,MET23,MET24-2,REC23,SEK24,SNT24,VIG23 | B:BLV24-ENG,CMS24,DFR24,EAS24,FFO24,MET23,MET24-2,REC23,SEK24,SNT24,VIG23 | C:AIF24,BLV24-ENG,CHK25,CMS24,DFR24,EAS24,FFO24,MET23,REC23,SEK24,SNT24,VIG23</t>
         </is>
       </c>
       <c r="T87" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="U87" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="88">
@@ -5160,17 +4307,6 @@
       <c r="H88" t="n">
         <v>0</v>
       </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr"/>
-      <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="inlineStr"/>
-      <c r="R88" t="inlineStr"/>
-      <c r="S88" t="inlineStr"/>
       <c r="T88" t="n">
         <v>0</v>
       </c>
@@ -5209,17 +4345,6 @@
       <c r="H89" t="n">
         <v>0</v>
       </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr"/>
-      <c r="P89" t="inlineStr"/>
-      <c r="Q89" t="inlineStr"/>
-      <c r="R89" t="inlineStr"/>
-      <c r="S89" t="inlineStr"/>
       <c r="T89" t="n">
         <v>0</v>
       </c>
@@ -5258,17 +4383,6 @@
       <c r="H90" t="n">
         <v>0</v>
       </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr"/>
-      <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="inlineStr"/>
-      <c r="R90" t="inlineStr"/>
-      <c r="S90" t="inlineStr"/>
       <c r="T90" t="n">
         <v>0</v>
       </c>
@@ -5317,32 +4431,21 @@
           <t>BLV24-ENG</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr">
         <is>
           <t>EAS24</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>VIG24</t>
-        </is>
-      </c>
-      <c r="O91" t="inlineStr"/>
-      <c r="P91" t="inlineStr"/>
-      <c r="Q91" t="inlineStr"/>
-      <c r="R91" t="inlineStr"/>
       <c r="S91" t="inlineStr">
         <is>
-          <t>A:BLV24-ENG,EAS24,VIG24 | B:EAS24,VIG24 | C:BLV24-ENG,EAS24,VIG24</t>
+          <t>A:BLV24-ENG,EAS24 | B:EAS24 | C:BLV24-ENG,EAS24</t>
         </is>
       </c>
       <c r="T91" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U91" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
@@ -5386,32 +4489,26 @@
           <t>AIF24</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr">
         <is>
           <t>BLV24-ENG</t>
         </is>
       </c>
-      <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr">
         <is>
-          <t>CHK24</t>
-        </is>
-      </c>
-      <c r="O92" t="inlineStr"/>
-      <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr"/>
-      <c r="R92" t="inlineStr"/>
+          <t>CHK25</t>
+        </is>
+      </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>A:AIF24,BLV24-ENG,CHK24,CHK25,CMS24,DFR24,EAS24,MET23,MET24-2,VIG23,VIG24,VIG24-2 | B:BLV24-ENG,CHK24,DFR24,EAS24,MET23,MET24-2,VIG23,VIG24,VIG24-2 | C:AIF24,BLV24-ENG,CHK24,CHK25,CMS24,DFR24,EAS24,MET23,VIG23,VIG24,VIG24-2</t>
+          <t>A:AIF24,BLV24-ENG,CHK25,CMS24,DFR24,EAS24,MET23,MET24-2,SEK24,VIG23 | B:BLV24-ENG,DFR24,EAS24,MET23,MET24-2,SEK24,VIG23 | C:AIF24,BLV24-ENG,CHK25,CMS24,DFR24,EAS24,MET23,SEK24,VIG23</t>
         </is>
       </c>
       <c r="T92" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="U92" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="93">
@@ -5445,17 +4542,6 @@
       <c r="H93" t="n">
         <v>0</v>
       </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
-      <c r="O93" t="inlineStr"/>
-      <c r="P93" t="inlineStr"/>
-      <c r="Q93" t="inlineStr"/>
-      <c r="R93" t="inlineStr"/>
-      <c r="S93" t="inlineStr"/>
       <c r="T93" t="n">
         <v>0</v>
       </c>
@@ -5504,25 +4590,19 @@
           <t>BLV24-ENG</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr">
         <is>
           <t>CHK25</t>
         </is>
       </c>
-      <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr">
         <is>
           <t>CMS24</t>
         </is>
       </c>
-      <c r="O94" t="inlineStr"/>
-      <c r="P94" t="inlineStr"/>
-      <c r="Q94" t="inlineStr"/>
-      <c r="R94" t="inlineStr"/>
       <c r="S94" t="inlineStr">
         <is>
-          <t>A:BLV24-ENG,CHK25,CMS24,EAS24,MET24-2,VIG24-2 | B:EAS24,MET24-2 | C:BLV24-ENG,CHK25,CMS24,EAS24,VIG24-2</t>
+          <t>A:BLV24-ENG,CHK25,CMS24,EAS24,MET24-2,SEK24 | B:EAS24,MET24-2 | C:BLV24-ENG,CHK25,CMS24,EAS24,SEK24</t>
         </is>
       </c>
       <c r="T94" t="n">
@@ -5563,17 +4643,6 @@
       <c r="H95" t="n">
         <v>0</v>
       </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
-      <c r="O95" t="inlineStr"/>
-      <c r="P95" t="inlineStr"/>
-      <c r="Q95" t="inlineStr"/>
-      <c r="R95" t="inlineStr"/>
-      <c r="S95" t="inlineStr"/>
       <c r="T95" t="n">
         <v>0</v>
       </c>
@@ -5622,14 +4691,6 @@
           <t>MET24-2</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
-      <c r="O96" t="inlineStr"/>
-      <c r="P96" t="inlineStr"/>
-      <c r="Q96" t="inlineStr"/>
-      <c r="R96" t="inlineStr"/>
       <c r="S96" t="inlineStr">
         <is>
           <t>A:MET24-2 | B:MET24-2</t>
@@ -5671,24 +4732,28 @@
         <v>45247</v>
       </c>
       <c r="H97" t="n">
-        <v>0</v>
-      </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
-      <c r="O97" t="inlineStr"/>
-      <c r="P97" t="inlineStr"/>
-      <c r="Q97" t="inlineStr"/>
-      <c r="R97" t="inlineStr"/>
-      <c r="S97" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>SEK24</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>A:SEK24</t>
+        </is>
+      </c>
       <c r="T97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
@@ -5722,17 +4787,6 @@
       <c r="H98" t="n">
         <v>0</v>
       </c>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
-      <c r="O98" t="inlineStr"/>
-      <c r="P98" t="inlineStr"/>
-      <c r="Q98" t="inlineStr"/>
-      <c r="R98" t="inlineStr"/>
-      <c r="S98" t="inlineStr"/>
       <c r="T98" t="n">
         <v>0</v>
       </c>
@@ -5771,17 +4825,6 @@
       <c r="H99" t="n">
         <v>0</v>
       </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr"/>
-      <c r="P99" t="inlineStr"/>
-      <c r="Q99" t="inlineStr"/>
-      <c r="R99" t="inlineStr"/>
-      <c r="S99" t="inlineStr"/>
       <c r="T99" t="n">
         <v>0</v>
       </c>
@@ -5820,17 +4863,6 @@
       <c r="H100" t="n">
         <v>0</v>
       </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
-      <c r="O100" t="inlineStr"/>
-      <c r="P100" t="inlineStr"/>
-      <c r="Q100" t="inlineStr"/>
-      <c r="R100" t="inlineStr"/>
-      <c r="S100" t="inlineStr"/>
       <c r="T100" t="n">
         <v>0</v>
       </c>
@@ -5869,17 +4901,6 @@
       <c r="H101" t="n">
         <v>0</v>
       </c>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
-      <c r="O101" t="inlineStr"/>
-      <c r="P101" t="inlineStr"/>
-      <c r="Q101" t="inlineStr"/>
-      <c r="R101" t="inlineStr"/>
-      <c r="S101" t="inlineStr"/>
       <c r="T101" t="n">
         <v>0</v>
       </c>
@@ -5916,36 +4937,13 @@
         <v>45247</v>
       </c>
       <c r="H102" t="n">
-        <v>2</v>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>ABC</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>VIG24</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
-      <c r="O102" t="inlineStr"/>
-      <c r="P102" t="inlineStr"/>
-      <c r="Q102" t="inlineStr"/>
-      <c r="R102" t="inlineStr"/>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>A:VIG24 | B:VIG24 | C:VIG24</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="T102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -5989,32 +4987,26 @@
           <t>BLV24-ENG</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr">
         <is>
           <t>CHK25</t>
         </is>
       </c>
-      <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr">
         <is>
           <t>CMS24</t>
         </is>
       </c>
-      <c r="O103" t="inlineStr"/>
-      <c r="P103" t="inlineStr"/>
-      <c r="Q103" t="inlineStr"/>
-      <c r="R103" t="inlineStr"/>
       <c r="S103" t="inlineStr">
         <is>
-          <t>A:BLV24-ENG,CHK25,CMS24,EAS24,MET23,MET24-2,VIG24 | B:EAS24,MET23,MET24-2,VIG24 | C:BLV24-ENG,CHK25,CMS24,EAS24,MET23,VIG24</t>
+          <t>A:BLV24-ENG,CHK25,CMS24,EAS24,MET23,MET24-2 | B:EAS24,MET23,MET24-2 | C:BLV24-ENG,CHK25,CMS24,EAS24,MET23</t>
         </is>
       </c>
       <c r="T103" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U103" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104">
@@ -6048,17 +5040,6 @@
       <c r="H104" t="n">
         <v>0</v>
       </c>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
-      <c r="O104" t="inlineStr"/>
-      <c r="P104" t="inlineStr"/>
-      <c r="Q104" t="inlineStr"/>
-      <c r="R104" t="inlineStr"/>
-      <c r="S104" t="inlineStr"/>
       <c r="T104" t="n">
         <v>0</v>
       </c>
@@ -6097,17 +5078,6 @@
       <c r="H105" t="n">
         <v>0</v>
       </c>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
-      <c r="O105" t="inlineStr"/>
-      <c r="P105" t="inlineStr"/>
-      <c r="Q105" t="inlineStr"/>
-      <c r="R105" t="inlineStr"/>
-      <c r="S105" t="inlineStr"/>
       <c r="T105" t="n">
         <v>0</v>
       </c>
@@ -6146,17 +5116,6 @@
       <c r="H106" t="n">
         <v>0</v>
       </c>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
-      <c r="O106" t="inlineStr"/>
-      <c r="P106" t="inlineStr"/>
-      <c r="Q106" t="inlineStr"/>
-      <c r="R106" t="inlineStr"/>
-      <c r="S106" t="inlineStr"/>
       <c r="T106" t="n">
         <v>0</v>
       </c>
@@ -6193,24 +5152,28 @@
         <v>45247</v>
       </c>
       <c r="H107" t="n">
-        <v>0</v>
-      </c>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
-      <c r="O107" t="inlineStr"/>
-      <c r="P107" t="inlineStr"/>
-      <c r="Q107" t="inlineStr"/>
-      <c r="R107" t="inlineStr"/>
-      <c r="S107" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>SEK24</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>A:SEK24</t>
+        </is>
+      </c>
       <c r="T107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
@@ -6244,17 +5207,6 @@
       <c r="H108" t="n">
         <v>0</v>
       </c>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
-      <c r="O108" t="inlineStr"/>
-      <c r="P108" t="inlineStr"/>
-      <c r="Q108" t="inlineStr"/>
-      <c r="R108" t="inlineStr"/>
-      <c r="S108" t="inlineStr"/>
       <c r="T108" t="n">
         <v>0</v>
       </c>
@@ -6293,17 +5245,6 @@
       <c r="H109" t="n">
         <v>0</v>
       </c>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
-      <c r="O109" t="inlineStr"/>
-      <c r="P109" t="inlineStr"/>
-      <c r="Q109" t="inlineStr"/>
-      <c r="R109" t="inlineStr"/>
-      <c r="S109" t="inlineStr"/>
       <c r="T109" t="n">
         <v>0</v>
       </c>
@@ -6342,17 +5283,6 @@
       <c r="H110" t="n">
         <v>0</v>
       </c>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
-      <c r="O110" t="inlineStr"/>
-      <c r="P110" t="inlineStr"/>
-      <c r="Q110" t="inlineStr"/>
-      <c r="R110" t="inlineStr"/>
-      <c r="S110" t="inlineStr"/>
       <c r="T110" t="n">
         <v>0</v>
       </c>
@@ -6391,17 +5321,6 @@
       <c r="H111" t="n">
         <v>0</v>
       </c>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
-      <c r="O111" t="inlineStr"/>
-      <c r="P111" t="inlineStr"/>
-      <c r="Q111" t="inlineStr"/>
-      <c r="R111" t="inlineStr"/>
-      <c r="S111" t="inlineStr"/>
       <c r="T111" t="n">
         <v>0</v>
       </c>
@@ -6440,17 +5359,6 @@
       <c r="H112" t="n">
         <v>0</v>
       </c>
-      <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
-      <c r="O112" t="inlineStr"/>
-      <c r="P112" t="inlineStr"/>
-      <c r="Q112" t="inlineStr"/>
-      <c r="R112" t="inlineStr"/>
-      <c r="S112" t="inlineStr"/>
       <c r="T112" t="n">
         <v>0</v>
       </c>
@@ -6489,17 +5397,6 @@
       <c r="H113" t="n">
         <v>0</v>
       </c>
-      <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
-      <c r="O113" t="inlineStr"/>
-      <c r="P113" t="inlineStr"/>
-      <c r="Q113" t="inlineStr"/>
-      <c r="R113" t="inlineStr"/>
-      <c r="S113" t="inlineStr"/>
       <c r="T113" t="n">
         <v>0</v>
       </c>
@@ -6548,32 +5445,26 @@
           <t>AIF24</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr">
         <is>
+          <t>AIF24-2</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
           <t>BLV24-ENG</t>
         </is>
       </c>
-      <c r="M114" t="inlineStr"/>
-      <c r="N114" t="inlineStr">
-        <is>
-          <t>CHK24</t>
-        </is>
-      </c>
-      <c r="O114" t="inlineStr"/>
-      <c r="P114" t="inlineStr"/>
-      <c r="Q114" t="inlineStr"/>
-      <c r="R114" t="inlineStr"/>
       <c r="S114" t="inlineStr">
         <is>
-          <t>A:AIF24,BLV24-ENG,CHK24,CHK25,CMS24,DFR24,EAS24,FFO24,HFL24,MET24,MET24-2,OAI24,SKY24,SNT24,VIG24,VIG24-2 | B:BLV24-ENG,CHK24,CMS24,DFR24,EAS24,FFO24,HFL24,MET24-2,SKY24,SNT24,VIG24 | C:AIF24,BLV24-ENG,CHK24,CHK25,CMS24,DFR24,EAS24,FFO24,HFL24,MET24,OAI24,SKY24,SNT24,VIG24,VIG24-2</t>
+          <t>A:AIF24,AIF24-2,BLV24-ENG,CHK25,CMS24,DFR24,EAS24,FFO24,HFL24,MET24,MET24-2,OAI24,REC23,SEK24,SKY24,SNT24 | B:BLV24-ENG,CMS24,DFR24,EAS24,FFO24,HFL24,MET24-2,REC23,SEK24,SKY24,SNT24 | C:AIF24,AIF24-2,BLV24-ENG,CHK25,CMS24,DFR24,EAS24,FFO24,HFL24,MET24,OAI24,REC23,SEK24,SKY24,SNT24</t>
         </is>
       </c>
       <c r="T114" t="n">
         <v>16</v>
       </c>
       <c r="U114" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="115">
@@ -6607,17 +5498,6 @@
       <c r="H115" t="n">
         <v>0</v>
       </c>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
-      <c r="O115" t="inlineStr"/>
-      <c r="P115" t="inlineStr"/>
-      <c r="Q115" t="inlineStr"/>
-      <c r="R115" t="inlineStr"/>
-      <c r="S115" t="inlineStr"/>
       <c r="T115" t="n">
         <v>0</v>
       </c>
@@ -6656,17 +5536,6 @@
       <c r="H116" t="n">
         <v>0</v>
       </c>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
-      <c r="O116" t="inlineStr"/>
-      <c r="P116" t="inlineStr"/>
-      <c r="Q116" t="inlineStr"/>
-      <c r="R116" t="inlineStr"/>
-      <c r="S116" t="inlineStr"/>
       <c r="T116" t="n">
         <v>0</v>
       </c>
@@ -6705,17 +5574,6 @@
       <c r="H117" t="n">
         <v>0</v>
       </c>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
-      <c r="O117" t="inlineStr"/>
-      <c r="P117" t="inlineStr"/>
-      <c r="Q117" t="inlineStr"/>
-      <c r="R117" t="inlineStr"/>
-      <c r="S117" t="inlineStr"/>
       <c r="T117" t="n">
         <v>0</v>
       </c>
@@ -6764,32 +5622,21 @@
           <t>BLV24-ENG</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr">
         <is>
           <t>EAS24</t>
         </is>
       </c>
-      <c r="M118" t="inlineStr"/>
-      <c r="N118" t="inlineStr">
-        <is>
-          <t>VIG24</t>
-        </is>
-      </c>
-      <c r="O118" t="inlineStr"/>
-      <c r="P118" t="inlineStr"/>
-      <c r="Q118" t="inlineStr"/>
-      <c r="R118" t="inlineStr"/>
       <c r="S118" t="inlineStr">
         <is>
-          <t>A:BLV24-ENG,EAS24,VIG24 | B:EAS24,VIG24 | C:BLV24-ENG,EAS24,VIG24</t>
+          <t>A:BLV24-ENG,EAS24 | B:EAS24 | C:BLV24-ENG,EAS24</t>
         </is>
       </c>
       <c r="T118" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U118" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="119">
@@ -6833,29 +5680,23 @@
           <t>AIF24</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr">
         <is>
+          <t>AIF24-2</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
           <t>BLV24-ENG</t>
         </is>
       </c>
-      <c r="M119" t="inlineStr"/>
-      <c r="N119" t="inlineStr">
-        <is>
-          <t>CHK24</t>
-        </is>
-      </c>
-      <c r="O119" t="inlineStr"/>
-      <c r="P119" t="inlineStr"/>
-      <c r="Q119" t="inlineStr"/>
-      <c r="R119" t="inlineStr"/>
       <c r="S119" t="inlineStr">
         <is>
-          <t>A:AIF24,BLV24-ENG,CHK24,CHK25,CMS24,DFR24,EAS24,HFL24,MET24,MET24-2,OAI24,SKY24,VIG24,VIG24-2 | B:BLV24-ENG,CHK24,DFR24,EAS24,HFL24,MET24-2,SKY24,VIG24,VIG24-2 | C:AIF24,BLV24-ENG,CHK24,CHK25,CMS24,DFR24,EAS24,HFL24,MET24,OAI24,SKY24,VIG24,VIG24-2</t>
+          <t>A:AIF24,AIF24-2,BLV24-ENG,CHK25,CMS24,DFR24,EAS24,HFL24,MET24,MET24-2,OAI24,SEK24,SKY24 | B:BLV24-ENG,DFR24,EAS24,HFL24,MET24-2,SEK24,SKY24 | C:AIF24,AIF24-2,BLV24-ENG,CHK25,CMS24,DFR24,EAS24,HFL24,MET24,OAI24,SEK24,SKY24</t>
         </is>
       </c>
       <c r="T119" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="U119" t="n">
         <v>11</v>
@@ -6892,17 +5733,6 @@
       <c r="H120" t="n">
         <v>0</v>
       </c>
-      <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
-      <c r="O120" t="inlineStr"/>
-      <c r="P120" t="inlineStr"/>
-      <c r="Q120" t="inlineStr"/>
-      <c r="R120" t="inlineStr"/>
-      <c r="S120" t="inlineStr"/>
       <c r="T120" t="n">
         <v>0</v>
       </c>
@@ -6948,35 +5778,29 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
+          <t>AIF24-2</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
           <t>BLV24-ENG</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr">
+      <c r="N121" t="inlineStr">
         <is>
           <t>CHK25</t>
         </is>
       </c>
-      <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr">
-        <is>
-          <t>CMS24</t>
-        </is>
-      </c>
-      <c r="O121" t="inlineStr"/>
-      <c r="P121" t="inlineStr"/>
-      <c r="Q121" t="inlineStr"/>
-      <c r="R121" t="inlineStr"/>
       <c r="S121" t="inlineStr">
         <is>
-          <t>A:BLV24-ENG,CHK25,CMS24,EAS24,MET24-2,OAI24,VIG24-2 | B:EAS24,MET24-2 | C:BLV24-ENG,CHK25,CMS24,EAS24,OAI24,VIG24-2</t>
+          <t>A:AIF24-2,BLV24-ENG,CHK25,CMS24,EAS24,MET24-2,OAI24,SEK24 | B:EAS24,MET24-2 | C:AIF24-2,BLV24-ENG,CHK25,CMS24,EAS24,OAI24,SEK24</t>
         </is>
       </c>
       <c r="T121" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U121" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="122">
@@ -7010,17 +5834,6 @@
       <c r="H122" t="n">
         <v>0</v>
       </c>
-      <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
-      <c r="O122" t="inlineStr"/>
-      <c r="P122" t="inlineStr"/>
-      <c r="Q122" t="inlineStr"/>
-      <c r="R122" t="inlineStr"/>
-      <c r="S122" t="inlineStr"/>
       <c r="T122" t="n">
         <v>0</v>
       </c>
@@ -7069,14 +5882,6 @@
           <t>MET24-2</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
-      <c r="O123" t="inlineStr"/>
-      <c r="P123" t="inlineStr"/>
-      <c r="Q123" t="inlineStr"/>
-      <c r="R123" t="inlineStr"/>
       <c r="S123" t="inlineStr">
         <is>
           <t>A:MET24-2 | B:MET24-2</t>
@@ -7118,24 +5923,28 @@
         <v>45421</v>
       </c>
       <c r="H124" t="n">
-        <v>0</v>
-      </c>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
-      <c r="O124" t="inlineStr"/>
-      <c r="P124" t="inlineStr"/>
-      <c r="Q124" t="inlineStr"/>
-      <c r="R124" t="inlineStr"/>
-      <c r="S124" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>SEK24</t>
+        </is>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>A:SEK24</t>
+        </is>
+      </c>
       <c r="T124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125">
@@ -7169,17 +5978,6 @@
       <c r="H125" t="n">
         <v>0</v>
       </c>
-      <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
-      <c r="O125" t="inlineStr"/>
-      <c r="P125" t="inlineStr"/>
-      <c r="Q125" t="inlineStr"/>
-      <c r="R125" t="inlineStr"/>
-      <c r="S125" t="inlineStr"/>
       <c r="T125" t="n">
         <v>0</v>
       </c>
@@ -7228,14 +6026,6 @@
           <t>HFL24</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
-      <c r="O126" t="inlineStr"/>
-      <c r="P126" t="inlineStr"/>
-      <c r="Q126" t="inlineStr"/>
-      <c r="R126" t="inlineStr"/>
       <c r="S126" t="inlineStr">
         <is>
           <t>A:HFL24</t>
@@ -7279,17 +6069,6 @@
       <c r="H127" t="n">
         <v>0</v>
       </c>
-      <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
-      <c r="O127" t="inlineStr"/>
-      <c r="P127" t="inlineStr"/>
-      <c r="Q127" t="inlineStr"/>
-      <c r="R127" t="inlineStr"/>
-      <c r="S127" t="inlineStr"/>
       <c r="T127" t="n">
         <v>0</v>
       </c>
@@ -7328,17 +6107,6 @@
       <c r="H128" t="n">
         <v>0</v>
       </c>
-      <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
-      <c r="O128" t="inlineStr"/>
-      <c r="P128" t="inlineStr"/>
-      <c r="Q128" t="inlineStr"/>
-      <c r="R128" t="inlineStr"/>
-      <c r="S128" t="inlineStr"/>
       <c r="T128" t="n">
         <v>0</v>
       </c>
@@ -7375,36 +6143,13 @@
         <v>45421</v>
       </c>
       <c r="H129" t="n">
-        <v>2</v>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>ABC</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>VIG24</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
-      <c r="O129" t="inlineStr"/>
-      <c r="P129" t="inlineStr"/>
-      <c r="Q129" t="inlineStr"/>
-      <c r="R129" t="inlineStr"/>
-      <c r="S129" t="inlineStr">
-        <is>
-          <t>A:VIG24 | B:VIG24 | C:VIG24</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="T129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -7445,28 +6190,22 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
+          <t>AIF24-2</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
           <t>BLV24-ENG</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr">
+      <c r="N130" t="inlineStr">
         <is>
           <t>CHK25</t>
         </is>
       </c>
-      <c r="M130" t="inlineStr"/>
-      <c r="N130" t="inlineStr">
-        <is>
-          <t>CMS24</t>
-        </is>
-      </c>
-      <c r="O130" t="inlineStr"/>
-      <c r="P130" t="inlineStr"/>
-      <c r="Q130" t="inlineStr"/>
-      <c r="R130" t="inlineStr"/>
       <c r="S130" t="inlineStr">
         <is>
-          <t>A:BLV24-ENG,CHK25,CMS24,EAS24,HFL24,MET24,MET24-2,OAI24,VIG24 | B:EAS24,MET24-2,VIG24 | C:BLV24-ENG,CHK25,CMS24,EAS24,HFL24,MET24,OAI24,VIG24</t>
+          <t>A:AIF24-2,BLV24-ENG,CHK25,CMS24,EAS24,HFL24,MET24,MET24-2,OAI24 | B:EAS24,MET24-2 | C:AIF24-2,BLV24-ENG,CHK25,CMS24,EAS24,HFL24,MET24,OAI24</t>
         </is>
       </c>
       <c r="T130" t="n">
@@ -7507,17 +6246,6 @@
       <c r="H131" t="n">
         <v>0</v>
       </c>
-      <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
-      <c r="O131" t="inlineStr"/>
-      <c r="P131" t="inlineStr"/>
-      <c r="Q131" t="inlineStr"/>
-      <c r="R131" t="inlineStr"/>
-      <c r="S131" t="inlineStr"/>
       <c r="T131" t="n">
         <v>0</v>
       </c>
@@ -7556,17 +6284,6 @@
       <c r="H132" t="n">
         <v>0</v>
       </c>
-      <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
-      <c r="O132" t="inlineStr"/>
-      <c r="P132" t="inlineStr"/>
-      <c r="Q132" t="inlineStr"/>
-      <c r="R132" t="inlineStr"/>
-      <c r="S132" t="inlineStr"/>
       <c r="T132" t="n">
         <v>0</v>
       </c>
@@ -7605,17 +6322,6 @@
       <c r="H133" t="n">
         <v>0</v>
       </c>
-      <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
-      <c r="O133" t="inlineStr"/>
-      <c r="P133" t="inlineStr"/>
-      <c r="Q133" t="inlineStr"/>
-      <c r="R133" t="inlineStr"/>
-      <c r="S133" t="inlineStr"/>
       <c r="T133" t="n">
         <v>0</v>
       </c>
@@ -7652,24 +6358,28 @@
         <v>45421</v>
       </c>
       <c r="H134" t="n">
-        <v>0</v>
-      </c>
-      <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
-      <c r="O134" t="inlineStr"/>
-      <c r="P134" t="inlineStr"/>
-      <c r="Q134" t="inlineStr"/>
-      <c r="R134" t="inlineStr"/>
-      <c r="S134" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>SEK24</t>
+        </is>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>A:SEK24</t>
+        </is>
+      </c>
       <c r="T134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
@@ -7703,17 +6413,6 @@
       <c r="H135" t="n">
         <v>0</v>
       </c>
-      <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
-      <c r="O135" t="inlineStr"/>
-      <c r="P135" t="inlineStr"/>
-      <c r="Q135" t="inlineStr"/>
-      <c r="R135" t="inlineStr"/>
-      <c r="S135" t="inlineStr"/>
       <c r="T135" t="n">
         <v>0</v>
       </c>
@@ -7752,17 +6451,6 @@
       <c r="H136" t="n">
         <v>0</v>
       </c>
-      <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
-      <c r="O136" t="inlineStr"/>
-      <c r="P136" t="inlineStr"/>
-      <c r="Q136" t="inlineStr"/>
-      <c r="R136" t="inlineStr"/>
-      <c r="S136" t="inlineStr"/>
       <c r="T136" t="n">
         <v>0</v>
       </c>
@@ -7801,17 +6489,6 @@
       <c r="H137" t="n">
         <v>0</v>
       </c>
-      <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
-      <c r="O137" t="inlineStr"/>
-      <c r="P137" t="inlineStr"/>
-      <c r="Q137" t="inlineStr"/>
-      <c r="R137" t="inlineStr"/>
-      <c r="S137" t="inlineStr"/>
       <c r="T137" t="n">
         <v>0</v>
       </c>
@@ -7850,17 +6527,6 @@
       <c r="H138" t="n">
         <v>0</v>
       </c>
-      <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
-      <c r="O138" t="inlineStr"/>
-      <c r="P138" t="inlineStr"/>
-      <c r="Q138" t="inlineStr"/>
-      <c r="R138" t="inlineStr"/>
-      <c r="S138" t="inlineStr"/>
       <c r="T138" t="n">
         <v>0</v>
       </c>
@@ -7899,17 +6565,6 @@
       <c r="H139" t="n">
         <v>0</v>
       </c>
-      <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
-      <c r="O139" t="inlineStr"/>
-      <c r="P139" t="inlineStr"/>
-      <c r="Q139" t="inlineStr"/>
-      <c r="R139" t="inlineStr"/>
-      <c r="S139" t="inlineStr"/>
       <c r="T139" t="n">
         <v>0</v>
       </c>
@@ -7948,17 +6603,6 @@
       <c r="H140" t="n">
         <v>0</v>
       </c>
-      <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
-      <c r="O140" t="inlineStr"/>
-      <c r="P140" t="inlineStr"/>
-      <c r="Q140" t="inlineStr"/>
-      <c r="R140" t="inlineStr"/>
-      <c r="S140" t="inlineStr"/>
       <c r="T140" t="n">
         <v>0</v>
       </c>
@@ -8004,28 +6648,22 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
+          <t>AIF24-2</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
           <t>BLV24-ENG</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr">
+      <c r="N141" t="inlineStr">
         <is>
           <t>CHK25</t>
         </is>
       </c>
-      <c r="M141" t="inlineStr"/>
-      <c r="N141" t="inlineStr">
-        <is>
-          <t>CMS24</t>
-        </is>
-      </c>
-      <c r="O141" t="inlineStr"/>
-      <c r="P141" t="inlineStr"/>
-      <c r="Q141" t="inlineStr"/>
-      <c r="R141" t="inlineStr"/>
       <c r="S141" t="inlineStr">
         <is>
-          <t>A:BLV24-ENG,CHK25,CMS24,EAS24,FFO24,HFL24,ISD25,MET24,MET24-2,MET25,REC25,VIG24-2 | B:BLV24-ENG,CMS24,EAS24,FFO24,HFL24,ISD25,MET24-2,REC25 | C:BLV24-ENG,CHK25,CMS24,EAS24,FFO24,HFL24,MET24,REC25,VIG24-2</t>
+          <t>A:AIF24-2,BLV24-ENG,CHK25,CMS24,EAS24,FFO24,HFL24,ISD25,MET24,MET24-2,MET25,REC25 | B:BLV24-ENG,CMS24,EAS24,FFO24,HFL24,ISD25,MET24-2,REC25 | C:AIF24-2,BLV24-ENG,CHK25,CMS24,EAS24,FFO24,HFL24,MET24,REC25</t>
         </is>
       </c>
       <c r="T141" t="n">
@@ -8066,17 +6704,6 @@
       <c r="H142" t="n">
         <v>0</v>
       </c>
-      <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr"/>
-      <c r="N142" t="inlineStr"/>
-      <c r="O142" t="inlineStr"/>
-      <c r="P142" t="inlineStr"/>
-      <c r="Q142" t="inlineStr"/>
-      <c r="R142" t="inlineStr"/>
-      <c r="S142" t="inlineStr"/>
       <c r="T142" t="n">
         <v>0</v>
       </c>
@@ -8115,17 +6742,6 @@
       <c r="H143" t="n">
         <v>0</v>
       </c>
-      <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr"/>
-      <c r="N143" t="inlineStr"/>
-      <c r="O143" t="inlineStr"/>
-      <c r="P143" t="inlineStr"/>
-      <c r="Q143" t="inlineStr"/>
-      <c r="R143" t="inlineStr"/>
-      <c r="S143" t="inlineStr"/>
       <c r="T143" t="n">
         <v>0</v>
       </c>
@@ -8164,17 +6780,6 @@
       <c r="H144" t="n">
         <v>0</v>
       </c>
-      <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr"/>
-      <c r="N144" t="inlineStr"/>
-      <c r="O144" t="inlineStr"/>
-      <c r="P144" t="inlineStr"/>
-      <c r="Q144" t="inlineStr"/>
-      <c r="R144" t="inlineStr"/>
-      <c r="S144" t="inlineStr"/>
       <c r="T144" t="n">
         <v>0</v>
       </c>
@@ -8223,18 +6828,11 @@
           <t>BLV24-ENG</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr">
         <is>
           <t>EAS24</t>
         </is>
       </c>
-      <c r="M145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
-      <c r="O145" t="inlineStr"/>
-      <c r="P145" t="inlineStr"/>
-      <c r="Q145" t="inlineStr"/>
-      <c r="R145" t="inlineStr"/>
       <c r="S145" t="inlineStr">
         <is>
           <t>A:BLV24-ENG,EAS24 | B:EAS24 | C:BLV24-ENG,EAS24</t>
@@ -8285,28 +6883,22 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
+          <t>AIF24-2</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
           <t>BLV24-ENG</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
-      <c r="L146" t="inlineStr">
+      <c r="N146" t="inlineStr">
         <is>
           <t>CHK25</t>
         </is>
       </c>
-      <c r="M146" t="inlineStr"/>
-      <c r="N146" t="inlineStr">
-        <is>
-          <t>CMS24</t>
-        </is>
-      </c>
-      <c r="O146" t="inlineStr"/>
-      <c r="P146" t="inlineStr"/>
-      <c r="Q146" t="inlineStr"/>
-      <c r="R146" t="inlineStr"/>
       <c r="S146" t="inlineStr">
         <is>
-          <t>A:BLV24-ENG,CHK25,CMS24,EAS24,HFL24,MET24,MET24-2,MET25,VIG24-2 | B:BLV24-ENG,EAS24,HFL24,MET24-2,VIG24-2 | C:BLV24-ENG,CHK25,CMS24,EAS24,HFL24,MET24,VIG24-2</t>
+          <t>A:AIF24-2,BLV24-ENG,CHK25,CMS24,EAS24,HFL24,MET24,MET24-2,MET25 | B:BLV24-ENG,EAS24,HFL24,MET24-2 | C:AIF24-2,BLV24-ENG,CHK25,CMS24,EAS24,HFL24,MET24</t>
         </is>
       </c>
       <c r="T146" t="n">
@@ -8347,17 +6939,6 @@
       <c r="H147" t="n">
         <v>0</v>
       </c>
-      <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
-      <c r="K147" t="inlineStr"/>
-      <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr"/>
-      <c r="N147" t="inlineStr"/>
-      <c r="O147" t="inlineStr"/>
-      <c r="P147" t="inlineStr"/>
-      <c r="Q147" t="inlineStr"/>
-      <c r="R147" t="inlineStr"/>
-      <c r="S147" t="inlineStr"/>
       <c r="T147" t="n">
         <v>0</v>
       </c>
@@ -8403,28 +6984,22 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
+          <t>AIF24-2</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
           <t>BLV24-ENG</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr">
+      <c r="N148" t="inlineStr">
         <is>
           <t>CHK25</t>
         </is>
       </c>
-      <c r="M148" t="inlineStr"/>
-      <c r="N148" t="inlineStr">
-        <is>
-          <t>CMS24</t>
-        </is>
-      </c>
-      <c r="O148" t="inlineStr"/>
-      <c r="P148" t="inlineStr"/>
-      <c r="Q148" t="inlineStr"/>
-      <c r="R148" t="inlineStr"/>
       <c r="S148" t="inlineStr">
         <is>
-          <t>A:BLV24-ENG,CHK25,CMS24,EAS24,MET24-2,VIG24-2 | B:EAS24,MET24-2 | C:BLV24-ENG,CHK25,CMS24,EAS24,VIG24-2</t>
+          <t>A:AIF24-2,BLV24-ENG,CHK25,CMS24,EAS24,MET24-2 | B:EAS24,MET24-2 | C:AIF24-2,BLV24-ENG,CHK25,CMS24,EAS24</t>
         </is>
       </c>
       <c r="T148" t="n">
@@ -8465,17 +7040,6 @@
       <c r="H149" t="n">
         <v>0</v>
       </c>
-      <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr"/>
-      <c r="N149" t="inlineStr"/>
-      <c r="O149" t="inlineStr"/>
-      <c r="P149" t="inlineStr"/>
-      <c r="Q149" t="inlineStr"/>
-      <c r="R149" t="inlineStr"/>
-      <c r="S149" t="inlineStr"/>
       <c r="T149" t="n">
         <v>0</v>
       </c>
@@ -8524,14 +7088,6 @@
           <t>MET24-2</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
-      <c r="O150" t="inlineStr"/>
-      <c r="P150" t="inlineStr"/>
-      <c r="Q150" t="inlineStr"/>
-      <c r="R150" t="inlineStr"/>
       <c r="S150" t="inlineStr">
         <is>
           <t>A:MET24-2 | B:MET24-2</t>
@@ -8575,17 +7131,6 @@
       <c r="H151" t="n">
         <v>0</v>
       </c>
-      <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr"/>
-      <c r="N151" t="inlineStr"/>
-      <c r="O151" t="inlineStr"/>
-      <c r="P151" t="inlineStr"/>
-      <c r="Q151" t="inlineStr"/>
-      <c r="R151" t="inlineStr"/>
-      <c r="S151" t="inlineStr"/>
       <c r="T151" t="n">
         <v>0</v>
       </c>
@@ -8624,17 +7169,6 @@
       <c r="H152" t="n">
         <v>0</v>
       </c>
-      <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr"/>
-      <c r="M152" t="inlineStr"/>
-      <c r="N152" t="inlineStr"/>
-      <c r="O152" t="inlineStr"/>
-      <c r="P152" t="inlineStr"/>
-      <c r="Q152" t="inlineStr"/>
-      <c r="R152" t="inlineStr"/>
-      <c r="S152" t="inlineStr"/>
       <c r="T152" t="n">
         <v>0</v>
       </c>
@@ -8683,14 +7217,6 @@
           <t>HFL24</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
-      <c r="L153" t="inlineStr"/>
-      <c r="M153" t="inlineStr"/>
-      <c r="N153" t="inlineStr"/>
-      <c r="O153" t="inlineStr"/>
-      <c r="P153" t="inlineStr"/>
-      <c r="Q153" t="inlineStr"/>
-      <c r="R153" t="inlineStr"/>
       <c r="S153" t="inlineStr">
         <is>
           <t>A:HFL24</t>
@@ -8734,17 +7260,6 @@
       <c r="H154" t="n">
         <v>0</v>
       </c>
-      <c r="I154" t="inlineStr"/>
-      <c r="J154" t="inlineStr"/>
-      <c r="K154" t="inlineStr"/>
-      <c r="L154" t="inlineStr"/>
-      <c r="M154" t="inlineStr"/>
-      <c r="N154" t="inlineStr"/>
-      <c r="O154" t="inlineStr"/>
-      <c r="P154" t="inlineStr"/>
-      <c r="Q154" t="inlineStr"/>
-      <c r="R154" t="inlineStr"/>
-      <c r="S154" t="inlineStr"/>
       <c r="T154" t="n">
         <v>0</v>
       </c>
@@ -8783,17 +7298,6 @@
       <c r="H155" t="n">
         <v>0</v>
       </c>
-      <c r="I155" t="inlineStr"/>
-      <c r="J155" t="inlineStr"/>
-      <c r="K155" t="inlineStr"/>
-      <c r="L155" t="inlineStr"/>
-      <c r="M155" t="inlineStr"/>
-      <c r="N155" t="inlineStr"/>
-      <c r="O155" t="inlineStr"/>
-      <c r="P155" t="inlineStr"/>
-      <c r="Q155" t="inlineStr"/>
-      <c r="R155" t="inlineStr"/>
-      <c r="S155" t="inlineStr"/>
       <c r="T155" t="n">
         <v>0</v>
       </c>
@@ -8832,17 +7336,6 @@
       <c r="H156" t="n">
         <v>0</v>
       </c>
-      <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
-      <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr"/>
-      <c r="M156" t="inlineStr"/>
-      <c r="N156" t="inlineStr"/>
-      <c r="O156" t="inlineStr"/>
-      <c r="P156" t="inlineStr"/>
-      <c r="Q156" t="inlineStr"/>
-      <c r="R156" t="inlineStr"/>
-      <c r="S156" t="inlineStr"/>
       <c r="T156" t="n">
         <v>0</v>
       </c>
@@ -8888,35 +7381,29 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
+          <t>AIF24-2</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
           <t>BLV24-ENG</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr">
+      <c r="N157" t="inlineStr">
         <is>
           <t>CHK25</t>
         </is>
       </c>
-      <c r="M157" t="inlineStr"/>
-      <c r="N157" t="inlineStr">
-        <is>
-          <t>CMS24</t>
-        </is>
-      </c>
-      <c r="O157" t="inlineStr"/>
-      <c r="P157" t="inlineStr"/>
-      <c r="Q157" t="inlineStr"/>
-      <c r="R157" t="inlineStr"/>
       <c r="S157" t="inlineStr">
         <is>
-          <t>A:BLV24-ENG,CHK25,CMS24,EAS24,HFL24,MET24,MET24-2,MET25 | B:EAS24,MET24-2 | C:BLV24-ENG,CHK25,CMS24,EAS24,HFL24,MET24</t>
+          <t>A:AIF24-2,BLV24-ENG,CHK25,CMS24,EAS24,HFL24,MET24,MET24-2,MET25 | B:EAS24,MET24-2 | C:AIF24-2,BLV24-ENG,CHK25,CMS24,EAS24,HFL24,MET24</t>
         </is>
       </c>
       <c r="T157" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U157" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="158">
@@ -8950,17 +7437,6 @@
       <c r="H158" t="n">
         <v>0</v>
       </c>
-      <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
-      <c r="K158" t="inlineStr"/>
-      <c r="L158" t="inlineStr"/>
-      <c r="M158" t="inlineStr"/>
-      <c r="N158" t="inlineStr"/>
-      <c r="O158" t="inlineStr"/>
-      <c r="P158" t="inlineStr"/>
-      <c r="Q158" t="inlineStr"/>
-      <c r="R158" t="inlineStr"/>
-      <c r="S158" t="inlineStr"/>
       <c r="T158" t="n">
         <v>0</v>
       </c>
@@ -8999,17 +7475,6 @@
       <c r="H159" t="n">
         <v>0</v>
       </c>
-      <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
-      <c r="K159" t="inlineStr"/>
-      <c r="L159" t="inlineStr"/>
-      <c r="M159" t="inlineStr"/>
-      <c r="N159" t="inlineStr"/>
-      <c r="O159" t="inlineStr"/>
-      <c r="P159" t="inlineStr"/>
-      <c r="Q159" t="inlineStr"/>
-      <c r="R159" t="inlineStr"/>
-      <c r="S159" t="inlineStr"/>
       <c r="T159" t="n">
         <v>0</v>
       </c>
@@ -9048,17 +7513,6 @@
       <c r="H160" t="n">
         <v>0</v>
       </c>
-      <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
-      <c r="K160" t="inlineStr"/>
-      <c r="L160" t="inlineStr"/>
-      <c r="M160" t="inlineStr"/>
-      <c r="N160" t="inlineStr"/>
-      <c r="O160" t="inlineStr"/>
-      <c r="P160" t="inlineStr"/>
-      <c r="Q160" t="inlineStr"/>
-      <c r="R160" t="inlineStr"/>
-      <c r="S160" t="inlineStr"/>
       <c r="T160" t="n">
         <v>0</v>
       </c>
@@ -9097,17 +7551,6 @@
       <c r="H161" t="n">
         <v>0</v>
       </c>
-      <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
-      <c r="K161" t="inlineStr"/>
-      <c r="L161" t="inlineStr"/>
-      <c r="M161" t="inlineStr"/>
-      <c r="N161" t="inlineStr"/>
-      <c r="O161" t="inlineStr"/>
-      <c r="P161" t="inlineStr"/>
-      <c r="Q161" t="inlineStr"/>
-      <c r="R161" t="inlineStr"/>
-      <c r="S161" t="inlineStr"/>
       <c r="T161" t="n">
         <v>0</v>
       </c>
@@ -9146,17 +7589,6 @@
       <c r="H162" t="n">
         <v>0</v>
       </c>
-      <c r="I162" t="inlineStr"/>
-      <c r="J162" t="inlineStr"/>
-      <c r="K162" t="inlineStr"/>
-      <c r="L162" t="inlineStr"/>
-      <c r="M162" t="inlineStr"/>
-      <c r="N162" t="inlineStr"/>
-      <c r="O162" t="inlineStr"/>
-      <c r="P162" t="inlineStr"/>
-      <c r="Q162" t="inlineStr"/>
-      <c r="R162" t="inlineStr"/>
-      <c r="S162" t="inlineStr"/>
       <c r="T162" t="n">
         <v>0</v>
       </c>
@@ -9195,17 +7627,6 @@
       <c r="H163" t="n">
         <v>0</v>
       </c>
-      <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
-      <c r="K163" t="inlineStr"/>
-      <c r="L163" t="inlineStr"/>
-      <c r="M163" t="inlineStr"/>
-      <c r="N163" t="inlineStr"/>
-      <c r="O163" t="inlineStr"/>
-      <c r="P163" t="inlineStr"/>
-      <c r="Q163" t="inlineStr"/>
-      <c r="R163" t="inlineStr"/>
-      <c r="S163" t="inlineStr"/>
       <c r="T163" t="n">
         <v>0</v>
       </c>
@@ -9244,17 +7665,6 @@
       <c r="H164" t="n">
         <v>0</v>
       </c>
-      <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
-      <c r="K164" t="inlineStr"/>
-      <c r="L164" t="inlineStr"/>
-      <c r="M164" t="inlineStr"/>
-      <c r="N164" t="inlineStr"/>
-      <c r="O164" t="inlineStr"/>
-      <c r="P164" t="inlineStr"/>
-      <c r="Q164" t="inlineStr"/>
-      <c r="R164" t="inlineStr"/>
-      <c r="S164" t="inlineStr"/>
       <c r="T164" t="n">
         <v>0</v>
       </c>
@@ -9293,17 +7703,6 @@
       <c r="H165" t="n">
         <v>0</v>
       </c>
-      <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
-      <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr"/>
-      <c r="M165" t="inlineStr"/>
-      <c r="N165" t="inlineStr"/>
-      <c r="O165" t="inlineStr"/>
-      <c r="P165" t="inlineStr"/>
-      <c r="Q165" t="inlineStr"/>
-      <c r="R165" t="inlineStr"/>
-      <c r="S165" t="inlineStr"/>
       <c r="T165" t="n">
         <v>0</v>
       </c>
@@ -9342,17 +7741,6 @@
       <c r="H166" t="n">
         <v>0</v>
       </c>
-      <c r="I166" t="inlineStr"/>
-      <c r="J166" t="inlineStr"/>
-      <c r="K166" t="inlineStr"/>
-      <c r="L166" t="inlineStr"/>
-      <c r="M166" t="inlineStr"/>
-      <c r="N166" t="inlineStr"/>
-      <c r="O166" t="inlineStr"/>
-      <c r="P166" t="inlineStr"/>
-      <c r="Q166" t="inlineStr"/>
-      <c r="R166" t="inlineStr"/>
-      <c r="S166" t="inlineStr"/>
       <c r="T166" t="n">
         <v>0</v>
       </c>
@@ -9391,17 +7779,6 @@
       <c r="H167" t="n">
         <v>0</v>
       </c>
-      <c r="I167" t="inlineStr"/>
-      <c r="J167" t="inlineStr"/>
-      <c r="K167" t="inlineStr"/>
-      <c r="L167" t="inlineStr"/>
-      <c r="M167" t="inlineStr"/>
-      <c r="N167" t="inlineStr"/>
-      <c r="O167" t="inlineStr"/>
-      <c r="P167" t="inlineStr"/>
-      <c r="Q167" t="inlineStr"/>
-      <c r="R167" t="inlineStr"/>
-      <c r="S167" t="inlineStr"/>
       <c r="T167" t="n">
         <v>0</v>
       </c>
@@ -9450,22 +7827,16 @@
           <t>CMS25-ENG</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr">
         <is>
           <t>ISD25</t>
         </is>
       </c>
-      <c r="M168" t="inlineStr"/>
       <c r="N168" t="inlineStr">
         <is>
           <t>MET24-2</t>
         </is>
       </c>
-      <c r="O168" t="inlineStr"/>
-      <c r="P168" t="inlineStr"/>
-      <c r="Q168" t="inlineStr"/>
-      <c r="R168" t="inlineStr"/>
       <c r="S168" t="inlineStr">
         <is>
           <t>A:CMS25-ENG,ISD25,MET24-2,MET25,REC25 | B:CMS25-ENG,ISD25,MET24-2,REC25 | C:CMS25-ENG,REC25</t>
@@ -9509,17 +7880,6 @@
       <c r="H169" t="n">
         <v>0</v>
       </c>
-      <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
-      <c r="K169" t="inlineStr"/>
-      <c r="L169" t="inlineStr"/>
-      <c r="M169" t="inlineStr"/>
-      <c r="N169" t="inlineStr"/>
-      <c r="O169" t="inlineStr"/>
-      <c r="P169" t="inlineStr"/>
-      <c r="Q169" t="inlineStr"/>
-      <c r="R169" t="inlineStr"/>
-      <c r="S169" t="inlineStr"/>
       <c r="T169" t="n">
         <v>0</v>
       </c>
@@ -9558,17 +7918,6 @@
       <c r="H170" t="n">
         <v>0</v>
       </c>
-      <c r="I170" t="inlineStr"/>
-      <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr"/>
-      <c r="L170" t="inlineStr"/>
-      <c r="M170" t="inlineStr"/>
-      <c r="N170" t="inlineStr"/>
-      <c r="O170" t="inlineStr"/>
-      <c r="P170" t="inlineStr"/>
-      <c r="Q170" t="inlineStr"/>
-      <c r="R170" t="inlineStr"/>
-      <c r="S170" t="inlineStr"/>
       <c r="T170" t="n">
         <v>0</v>
       </c>
@@ -9607,17 +7956,6 @@
       <c r="H171" t="n">
         <v>0</v>
       </c>
-      <c r="I171" t="inlineStr"/>
-      <c r="J171" t="inlineStr"/>
-      <c r="K171" t="inlineStr"/>
-      <c r="L171" t="inlineStr"/>
-      <c r="M171" t="inlineStr"/>
-      <c r="N171" t="inlineStr"/>
-      <c r="O171" t="inlineStr"/>
-      <c r="P171" t="inlineStr"/>
-      <c r="Q171" t="inlineStr"/>
-      <c r="R171" t="inlineStr"/>
-      <c r="S171" t="inlineStr"/>
       <c r="T171" t="n">
         <v>0</v>
       </c>
@@ -9656,17 +7994,6 @@
       <c r="H172" t="n">
         <v>0</v>
       </c>
-      <c r="I172" t="inlineStr"/>
-      <c r="J172" t="inlineStr"/>
-      <c r="K172" t="inlineStr"/>
-      <c r="L172" t="inlineStr"/>
-      <c r="M172" t="inlineStr"/>
-      <c r="N172" t="inlineStr"/>
-      <c r="O172" t="inlineStr"/>
-      <c r="P172" t="inlineStr"/>
-      <c r="Q172" t="inlineStr"/>
-      <c r="R172" t="inlineStr"/>
-      <c r="S172" t="inlineStr"/>
       <c r="T172" t="n">
         <v>0</v>
       </c>
@@ -9715,18 +8042,11 @@
           <t>MET24-2</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
       <c r="L173" t="inlineStr">
         <is>
           <t>MET25</t>
         </is>
       </c>
-      <c r="M173" t="inlineStr"/>
-      <c r="N173" t="inlineStr"/>
-      <c r="O173" t="inlineStr"/>
-      <c r="P173" t="inlineStr"/>
-      <c r="Q173" t="inlineStr"/>
-      <c r="R173" t="inlineStr"/>
       <c r="S173" t="inlineStr">
         <is>
           <t>A:MET24-2,MET25 | B:MET24-2</t>
@@ -9770,17 +8090,6 @@
       <c r="H174" t="n">
         <v>0</v>
       </c>
-      <c r="I174" t="inlineStr"/>
-      <c r="J174" t="inlineStr"/>
-      <c r="K174" t="inlineStr"/>
-      <c r="L174" t="inlineStr"/>
-      <c r="M174" t="inlineStr"/>
-      <c r="N174" t="inlineStr"/>
-      <c r="O174" t="inlineStr"/>
-      <c r="P174" t="inlineStr"/>
-      <c r="Q174" t="inlineStr"/>
-      <c r="R174" t="inlineStr"/>
-      <c r="S174" t="inlineStr"/>
       <c r="T174" t="n">
         <v>0</v>
       </c>
@@ -9829,14 +8138,6 @@
           <t>MET24-2</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
-      <c r="L175" t="inlineStr"/>
-      <c r="M175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
-      <c r="O175" t="inlineStr"/>
-      <c r="P175" t="inlineStr"/>
-      <c r="Q175" t="inlineStr"/>
-      <c r="R175" t="inlineStr"/>
       <c r="S175" t="inlineStr">
         <is>
           <t>A:MET24-2 | B:MET24-2</t>
@@ -9880,17 +8181,6 @@
       <c r="H176" t="n">
         <v>0</v>
       </c>
-      <c r="I176" t="inlineStr"/>
-      <c r="J176" t="inlineStr"/>
-      <c r="K176" t="inlineStr"/>
-      <c r="L176" t="inlineStr"/>
-      <c r="M176" t="inlineStr"/>
-      <c r="N176" t="inlineStr"/>
-      <c r="O176" t="inlineStr"/>
-      <c r="P176" t="inlineStr"/>
-      <c r="Q176" t="inlineStr"/>
-      <c r="R176" t="inlineStr"/>
-      <c r="S176" t="inlineStr"/>
       <c r="T176" t="n">
         <v>0</v>
       </c>
@@ -9939,14 +8229,6 @@
           <t>MET24-2</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
-      <c r="L177" t="inlineStr"/>
-      <c r="M177" t="inlineStr"/>
-      <c r="N177" t="inlineStr"/>
-      <c r="O177" t="inlineStr"/>
-      <c r="P177" t="inlineStr"/>
-      <c r="Q177" t="inlineStr"/>
-      <c r="R177" t="inlineStr"/>
       <c r="S177" t="inlineStr">
         <is>
           <t>A:MET24-2 | B:MET24-2</t>
@@ -9990,17 +8272,6 @@
       <c r="H178" t="n">
         <v>0</v>
       </c>
-      <c r="I178" t="inlineStr"/>
-      <c r="J178" t="inlineStr"/>
-      <c r="K178" t="inlineStr"/>
-      <c r="L178" t="inlineStr"/>
-      <c r="M178" t="inlineStr"/>
-      <c r="N178" t="inlineStr"/>
-      <c r="O178" t="inlineStr"/>
-      <c r="P178" t="inlineStr"/>
-      <c r="Q178" t="inlineStr"/>
-      <c r="R178" t="inlineStr"/>
-      <c r="S178" t="inlineStr"/>
       <c r="T178" t="n">
         <v>0</v>
       </c>
@@ -10039,17 +8310,6 @@
       <c r="H179" t="n">
         <v>0</v>
       </c>
-      <c r="I179" t="inlineStr"/>
-      <c r="J179" t="inlineStr"/>
-      <c r="K179" t="inlineStr"/>
-      <c r="L179" t="inlineStr"/>
-      <c r="M179" t="inlineStr"/>
-      <c r="N179" t="inlineStr"/>
-      <c r="O179" t="inlineStr"/>
-      <c r="P179" t="inlineStr"/>
-      <c r="Q179" t="inlineStr"/>
-      <c r="R179" t="inlineStr"/>
-      <c r="S179" t="inlineStr"/>
       <c r="T179" t="n">
         <v>0</v>
       </c>
@@ -10088,17 +8348,6 @@
       <c r="H180" t="n">
         <v>0</v>
       </c>
-      <c r="I180" t="inlineStr"/>
-      <c r="J180" t="inlineStr"/>
-      <c r="K180" t="inlineStr"/>
-      <c r="L180" t="inlineStr"/>
-      <c r="M180" t="inlineStr"/>
-      <c r="N180" t="inlineStr"/>
-      <c r="O180" t="inlineStr"/>
-      <c r="P180" t="inlineStr"/>
-      <c r="Q180" t="inlineStr"/>
-      <c r="R180" t="inlineStr"/>
-      <c r="S180" t="inlineStr"/>
       <c r="T180" t="n">
         <v>0</v>
       </c>
@@ -10137,17 +8386,6 @@
       <c r="H181" t="n">
         <v>0</v>
       </c>
-      <c r="I181" t="inlineStr"/>
-      <c r="J181" t="inlineStr"/>
-      <c r="K181" t="inlineStr"/>
-      <c r="L181" t="inlineStr"/>
-      <c r="M181" t="inlineStr"/>
-      <c r="N181" t="inlineStr"/>
-      <c r="O181" t="inlineStr"/>
-      <c r="P181" t="inlineStr"/>
-      <c r="Q181" t="inlineStr"/>
-      <c r="R181" t="inlineStr"/>
-      <c r="S181" t="inlineStr"/>
       <c r="T181" t="n">
         <v>0</v>
       </c>
@@ -10186,17 +8424,6 @@
       <c r="H182" t="n">
         <v>0</v>
       </c>
-      <c r="I182" t="inlineStr"/>
-      <c r="J182" t="inlineStr"/>
-      <c r="K182" t="inlineStr"/>
-      <c r="L182" t="inlineStr"/>
-      <c r="M182" t="inlineStr"/>
-      <c r="N182" t="inlineStr"/>
-      <c r="O182" t="inlineStr"/>
-      <c r="P182" t="inlineStr"/>
-      <c r="Q182" t="inlineStr"/>
-      <c r="R182" t="inlineStr"/>
-      <c r="S182" t="inlineStr"/>
       <c r="T182" t="n">
         <v>0</v>
       </c>
@@ -10235,17 +8462,6 @@
       <c r="H183" t="n">
         <v>0</v>
       </c>
-      <c r="I183" t="inlineStr"/>
-      <c r="J183" t="inlineStr"/>
-      <c r="K183" t="inlineStr"/>
-      <c r="L183" t="inlineStr"/>
-      <c r="M183" t="inlineStr"/>
-      <c r="N183" t="inlineStr"/>
-      <c r="O183" t="inlineStr"/>
-      <c r="P183" t="inlineStr"/>
-      <c r="Q183" t="inlineStr"/>
-      <c r="R183" t="inlineStr"/>
-      <c r="S183" t="inlineStr"/>
       <c r="T183" t="n">
         <v>0</v>
       </c>
@@ -10294,18 +8510,11 @@
           <t>MET24-2</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
       <c r="L184" t="inlineStr">
         <is>
           <t>MET25</t>
         </is>
       </c>
-      <c r="M184" t="inlineStr"/>
-      <c r="N184" t="inlineStr"/>
-      <c r="O184" t="inlineStr"/>
-      <c r="P184" t="inlineStr"/>
-      <c r="Q184" t="inlineStr"/>
-      <c r="R184" t="inlineStr"/>
       <c r="S184" t="inlineStr">
         <is>
           <t>A:MET24-2,MET25 | B:MET24-2</t>
@@ -10349,17 +8558,6 @@
       <c r="H185" t="n">
         <v>0</v>
       </c>
-      <c r="I185" t="inlineStr"/>
-      <c r="J185" t="inlineStr"/>
-      <c r="K185" t="inlineStr"/>
-      <c r="L185" t="inlineStr"/>
-      <c r="M185" t="inlineStr"/>
-      <c r="N185" t="inlineStr"/>
-      <c r="O185" t="inlineStr"/>
-      <c r="P185" t="inlineStr"/>
-      <c r="Q185" t="inlineStr"/>
-      <c r="R185" t="inlineStr"/>
-      <c r="S185" t="inlineStr"/>
       <c r="T185" t="n">
         <v>0</v>
       </c>
@@ -10398,17 +8596,6 @@
       <c r="H186" t="n">
         <v>0</v>
       </c>
-      <c r="I186" t="inlineStr"/>
-      <c r="J186" t="inlineStr"/>
-      <c r="K186" t="inlineStr"/>
-      <c r="L186" t="inlineStr"/>
-      <c r="M186" t="inlineStr"/>
-      <c r="N186" t="inlineStr"/>
-      <c r="O186" t="inlineStr"/>
-      <c r="P186" t="inlineStr"/>
-      <c r="Q186" t="inlineStr"/>
-      <c r="R186" t="inlineStr"/>
-      <c r="S186" t="inlineStr"/>
       <c r="T186" t="n">
         <v>0</v>
       </c>
@@ -10447,17 +8634,6 @@
       <c r="H187" t="n">
         <v>0</v>
       </c>
-      <c r="I187" t="inlineStr"/>
-      <c r="J187" t="inlineStr"/>
-      <c r="K187" t="inlineStr"/>
-      <c r="L187" t="inlineStr"/>
-      <c r="M187" t="inlineStr"/>
-      <c r="N187" t="inlineStr"/>
-      <c r="O187" t="inlineStr"/>
-      <c r="P187" t="inlineStr"/>
-      <c r="Q187" t="inlineStr"/>
-      <c r="R187" t="inlineStr"/>
-      <c r="S187" t="inlineStr"/>
       <c r="T187" t="n">
         <v>0</v>
       </c>
@@ -10496,17 +8672,6 @@
       <c r="H188" t="n">
         <v>0</v>
       </c>
-      <c r="I188" t="inlineStr"/>
-      <c r="J188" t="inlineStr"/>
-      <c r="K188" t="inlineStr"/>
-      <c r="L188" t="inlineStr"/>
-      <c r="M188" t="inlineStr"/>
-      <c r="N188" t="inlineStr"/>
-      <c r="O188" t="inlineStr"/>
-      <c r="P188" t="inlineStr"/>
-      <c r="Q188" t="inlineStr"/>
-      <c r="R188" t="inlineStr"/>
-      <c r="S188" t="inlineStr"/>
       <c r="T188" t="n">
         <v>0</v>
       </c>
@@ -10545,17 +8710,6 @@
       <c r="H189" t="n">
         <v>0</v>
       </c>
-      <c r="I189" t="inlineStr"/>
-      <c r="J189" t="inlineStr"/>
-      <c r="K189" t="inlineStr"/>
-      <c r="L189" t="inlineStr"/>
-      <c r="M189" t="inlineStr"/>
-      <c r="N189" t="inlineStr"/>
-      <c r="O189" t="inlineStr"/>
-      <c r="P189" t="inlineStr"/>
-      <c r="Q189" t="inlineStr"/>
-      <c r="R189" t="inlineStr"/>
-      <c r="S189" t="inlineStr"/>
       <c r="T189" t="n">
         <v>0</v>
       </c>
@@ -10594,17 +8748,6 @@
       <c r="H190" t="n">
         <v>0</v>
       </c>
-      <c r="I190" t="inlineStr"/>
-      <c r="J190" t="inlineStr"/>
-      <c r="K190" t="inlineStr"/>
-      <c r="L190" t="inlineStr"/>
-      <c r="M190" t="inlineStr"/>
-      <c r="N190" t="inlineStr"/>
-      <c r="O190" t="inlineStr"/>
-      <c r="P190" t="inlineStr"/>
-      <c r="Q190" t="inlineStr"/>
-      <c r="R190" t="inlineStr"/>
-      <c r="S190" t="inlineStr"/>
       <c r="T190" t="n">
         <v>0</v>
       </c>
@@ -10643,17 +8786,6 @@
       <c r="H191" t="n">
         <v>0</v>
       </c>
-      <c r="I191" t="inlineStr"/>
-      <c r="J191" t="inlineStr"/>
-      <c r="K191" t="inlineStr"/>
-      <c r="L191" t="inlineStr"/>
-      <c r="M191" t="inlineStr"/>
-      <c r="N191" t="inlineStr"/>
-      <c r="O191" t="inlineStr"/>
-      <c r="P191" t="inlineStr"/>
-      <c r="Q191" t="inlineStr"/>
-      <c r="R191" t="inlineStr"/>
-      <c r="S191" t="inlineStr"/>
       <c r="T191" t="n">
         <v>0</v>
       </c>
@@ -10692,17 +8824,6 @@
       <c r="H192" t="n">
         <v>0</v>
       </c>
-      <c r="I192" t="inlineStr"/>
-      <c r="J192" t="inlineStr"/>
-      <c r="K192" t="inlineStr"/>
-      <c r="L192" t="inlineStr"/>
-      <c r="M192" t="inlineStr"/>
-      <c r="N192" t="inlineStr"/>
-      <c r="O192" t="inlineStr"/>
-      <c r="P192" t="inlineStr"/>
-      <c r="Q192" t="inlineStr"/>
-      <c r="R192" t="inlineStr"/>
-      <c r="S192" t="inlineStr"/>
       <c r="T192" t="n">
         <v>0</v>
       </c>
@@ -10741,17 +8862,6 @@
       <c r="H193" t="n">
         <v>0</v>
       </c>
-      <c r="I193" t="inlineStr"/>
-      <c r="J193" t="inlineStr"/>
-      <c r="K193" t="inlineStr"/>
-      <c r="L193" t="inlineStr"/>
-      <c r="M193" t="inlineStr"/>
-      <c r="N193" t="inlineStr"/>
-      <c r="O193" t="inlineStr"/>
-      <c r="P193" t="inlineStr"/>
-      <c r="Q193" t="inlineStr"/>
-      <c r="R193" t="inlineStr"/>
-      <c r="S193" t="inlineStr"/>
       <c r="T193" t="n">
         <v>0</v>
       </c>
@@ -10790,17 +8900,6 @@
       <c r="H194" t="n">
         <v>0</v>
       </c>
-      <c r="I194" t="inlineStr"/>
-      <c r="J194" t="inlineStr"/>
-      <c r="K194" t="inlineStr"/>
-      <c r="L194" t="inlineStr"/>
-      <c r="M194" t="inlineStr"/>
-      <c r="N194" t="inlineStr"/>
-      <c r="O194" t="inlineStr"/>
-      <c r="P194" t="inlineStr"/>
-      <c r="Q194" t="inlineStr"/>
-      <c r="R194" t="inlineStr"/>
-      <c r="S194" t="inlineStr"/>
       <c r="T194" t="n">
         <v>0</v>
       </c>
@@ -10839,17 +8938,6 @@
       <c r="H195" t="n">
         <v>0</v>
       </c>
-      <c r="I195" t="inlineStr"/>
-      <c r="J195" t="inlineStr"/>
-      <c r="K195" t="inlineStr"/>
-      <c r="L195" t="inlineStr"/>
-      <c r="M195" t="inlineStr"/>
-      <c r="N195" t="inlineStr"/>
-      <c r="O195" t="inlineStr"/>
-      <c r="P195" t="inlineStr"/>
-      <c r="Q195" t="inlineStr"/>
-      <c r="R195" t="inlineStr"/>
-      <c r="S195" t="inlineStr"/>
       <c r="T195" t="n">
         <v>0</v>
       </c>
@@ -10888,17 +8976,6 @@
       <c r="H196" t="n">
         <v>0</v>
       </c>
-      <c r="I196" t="inlineStr"/>
-      <c r="J196" t="inlineStr"/>
-      <c r="K196" t="inlineStr"/>
-      <c r="L196" t="inlineStr"/>
-      <c r="M196" t="inlineStr"/>
-      <c r="N196" t="inlineStr"/>
-      <c r="O196" t="inlineStr"/>
-      <c r="P196" t="inlineStr"/>
-      <c r="Q196" t="inlineStr"/>
-      <c r="R196" t="inlineStr"/>
-      <c r="S196" t="inlineStr"/>
       <c r="T196" t="n">
         <v>0</v>
       </c>
@@ -10937,17 +9014,6 @@
       <c r="H197" t="n">
         <v>0</v>
       </c>
-      <c r="I197" t="inlineStr"/>
-      <c r="J197" t="inlineStr"/>
-      <c r="K197" t="inlineStr"/>
-      <c r="L197" t="inlineStr"/>
-      <c r="M197" t="inlineStr"/>
-      <c r="N197" t="inlineStr"/>
-      <c r="O197" t="inlineStr"/>
-      <c r="P197" t="inlineStr"/>
-      <c r="Q197" t="inlineStr"/>
-      <c r="R197" t="inlineStr"/>
-      <c r="S197" t="inlineStr"/>
       <c r="T197" t="n">
         <v>0</v>
       </c>
@@ -10986,17 +9052,6 @@
       <c r="H198" t="n">
         <v>0</v>
       </c>
-      <c r="I198" t="inlineStr"/>
-      <c r="J198" t="inlineStr"/>
-      <c r="K198" t="inlineStr"/>
-      <c r="L198" t="inlineStr"/>
-      <c r="M198" t="inlineStr"/>
-      <c r="N198" t="inlineStr"/>
-      <c r="O198" t="inlineStr"/>
-      <c r="P198" t="inlineStr"/>
-      <c r="Q198" t="inlineStr"/>
-      <c r="R198" t="inlineStr"/>
-      <c r="S198" t="inlineStr"/>
       <c r="T198" t="n">
         <v>0</v>
       </c>
@@ -11035,17 +9090,6 @@
       <c r="H199" t="n">
         <v>0</v>
       </c>
-      <c r="I199" t="inlineStr"/>
-      <c r="J199" t="inlineStr"/>
-      <c r="K199" t="inlineStr"/>
-      <c r="L199" t="inlineStr"/>
-      <c r="M199" t="inlineStr"/>
-      <c r="N199" t="inlineStr"/>
-      <c r="O199" t="inlineStr"/>
-      <c r="P199" t="inlineStr"/>
-      <c r="Q199" t="inlineStr"/>
-      <c r="R199" t="inlineStr"/>
-      <c r="S199" t="inlineStr"/>
       <c r="T199" t="n">
         <v>0</v>
       </c>
@@ -11084,17 +9128,6 @@
       <c r="H200" t="n">
         <v>0</v>
       </c>
-      <c r="I200" t="inlineStr"/>
-      <c r="J200" t="inlineStr"/>
-      <c r="K200" t="inlineStr"/>
-      <c r="L200" t="inlineStr"/>
-      <c r="M200" t="inlineStr"/>
-      <c r="N200" t="inlineStr"/>
-      <c r="O200" t="inlineStr"/>
-      <c r="P200" t="inlineStr"/>
-      <c r="Q200" t="inlineStr"/>
-      <c r="R200" t="inlineStr"/>
-      <c r="S200" t="inlineStr"/>
       <c r="T200" t="n">
         <v>0</v>
       </c>
@@ -11133,17 +9166,6 @@
       <c r="H201" t="n">
         <v>0</v>
       </c>
-      <c r="I201" t="inlineStr"/>
-      <c r="J201" t="inlineStr"/>
-      <c r="K201" t="inlineStr"/>
-      <c r="L201" t="inlineStr"/>
-      <c r="M201" t="inlineStr"/>
-      <c r="N201" t="inlineStr"/>
-      <c r="O201" t="inlineStr"/>
-      <c r="P201" t="inlineStr"/>
-      <c r="Q201" t="inlineStr"/>
-      <c r="R201" t="inlineStr"/>
-      <c r="S201" t="inlineStr"/>
       <c r="T201" t="n">
         <v>0</v>
       </c>
@@ -11182,17 +9204,6 @@
       <c r="H202" t="n">
         <v>0</v>
       </c>
-      <c r="I202" t="inlineStr"/>
-      <c r="J202" t="inlineStr"/>
-      <c r="K202" t="inlineStr"/>
-      <c r="L202" t="inlineStr"/>
-      <c r="M202" t="inlineStr"/>
-      <c r="N202" t="inlineStr"/>
-      <c r="O202" t="inlineStr"/>
-      <c r="P202" t="inlineStr"/>
-      <c r="Q202" t="inlineStr"/>
-      <c r="R202" t="inlineStr"/>
-      <c r="S202" t="inlineStr"/>
       <c r="T202" t="n">
         <v>0</v>
       </c>
@@ -11231,17 +9242,6 @@
       <c r="H203" t="n">
         <v>0</v>
       </c>
-      <c r="I203" t="inlineStr"/>
-      <c r="J203" t="inlineStr"/>
-      <c r="K203" t="inlineStr"/>
-      <c r="L203" t="inlineStr"/>
-      <c r="M203" t="inlineStr"/>
-      <c r="N203" t="inlineStr"/>
-      <c r="O203" t="inlineStr"/>
-      <c r="P203" t="inlineStr"/>
-      <c r="Q203" t="inlineStr"/>
-      <c r="R203" t="inlineStr"/>
-      <c r="S203" t="inlineStr"/>
       <c r="T203" t="n">
         <v>0</v>
       </c>
@@ -11280,17 +9280,6 @@
       <c r="H204" t="n">
         <v>0</v>
       </c>
-      <c r="I204" t="inlineStr"/>
-      <c r="J204" t="inlineStr"/>
-      <c r="K204" t="inlineStr"/>
-      <c r="L204" t="inlineStr"/>
-      <c r="M204" t="inlineStr"/>
-      <c r="N204" t="inlineStr"/>
-      <c r="O204" t="inlineStr"/>
-      <c r="P204" t="inlineStr"/>
-      <c r="Q204" t="inlineStr"/>
-      <c r="R204" t="inlineStr"/>
-      <c r="S204" t="inlineStr"/>
       <c r="T204" t="n">
         <v>0</v>
       </c>
@@ -11329,17 +9318,6 @@
       <c r="H205" t="n">
         <v>0</v>
       </c>
-      <c r="I205" t="inlineStr"/>
-      <c r="J205" t="inlineStr"/>
-      <c r="K205" t="inlineStr"/>
-      <c r="L205" t="inlineStr"/>
-      <c r="M205" t="inlineStr"/>
-      <c r="N205" t="inlineStr"/>
-      <c r="O205" t="inlineStr"/>
-      <c r="P205" t="inlineStr"/>
-      <c r="Q205" t="inlineStr"/>
-      <c r="R205" t="inlineStr"/>
-      <c r="S205" t="inlineStr"/>
       <c r="T205" t="n">
         <v>0</v>
       </c>
@@ -11378,17 +9356,6 @@
       <c r="H206" t="n">
         <v>0</v>
       </c>
-      <c r="I206" t="inlineStr"/>
-      <c r="J206" t="inlineStr"/>
-      <c r="K206" t="inlineStr"/>
-      <c r="L206" t="inlineStr"/>
-      <c r="M206" t="inlineStr"/>
-      <c r="N206" t="inlineStr"/>
-      <c r="O206" t="inlineStr"/>
-      <c r="P206" t="inlineStr"/>
-      <c r="Q206" t="inlineStr"/>
-      <c r="R206" t="inlineStr"/>
-      <c r="S206" t="inlineStr"/>
       <c r="T206" t="n">
         <v>0</v>
       </c>
@@ -11427,17 +9394,6 @@
       <c r="H207" t="n">
         <v>0</v>
       </c>
-      <c r="I207" t="inlineStr"/>
-      <c r="J207" t="inlineStr"/>
-      <c r="K207" t="inlineStr"/>
-      <c r="L207" t="inlineStr"/>
-      <c r="M207" t="inlineStr"/>
-      <c r="N207" t="inlineStr"/>
-      <c r="O207" t="inlineStr"/>
-      <c r="P207" t="inlineStr"/>
-      <c r="Q207" t="inlineStr"/>
-      <c r="R207" t="inlineStr"/>
-      <c r="S207" t="inlineStr"/>
       <c r="T207" t="n">
         <v>0</v>
       </c>
@@ -11476,17 +9432,6 @@
       <c r="H208" t="n">
         <v>0</v>
       </c>
-      <c r="I208" t="inlineStr"/>
-      <c r="J208" t="inlineStr"/>
-      <c r="K208" t="inlineStr"/>
-      <c r="L208" t="inlineStr"/>
-      <c r="M208" t="inlineStr"/>
-      <c r="N208" t="inlineStr"/>
-      <c r="O208" t="inlineStr"/>
-      <c r="P208" t="inlineStr"/>
-      <c r="Q208" t="inlineStr"/>
-      <c r="R208" t="inlineStr"/>
-      <c r="S208" t="inlineStr"/>
       <c r="T208" t="n">
         <v>0</v>
       </c>
@@ -11525,17 +9470,6 @@
       <c r="H209" t="n">
         <v>0</v>
       </c>
-      <c r="I209" t="inlineStr"/>
-      <c r="J209" t="inlineStr"/>
-      <c r="K209" t="inlineStr"/>
-      <c r="L209" t="inlineStr"/>
-      <c r="M209" t="inlineStr"/>
-      <c r="N209" t="inlineStr"/>
-      <c r="O209" t="inlineStr"/>
-      <c r="P209" t="inlineStr"/>
-      <c r="Q209" t="inlineStr"/>
-      <c r="R209" t="inlineStr"/>
-      <c r="S209" t="inlineStr"/>
       <c r="T209" t="n">
         <v>0</v>
       </c>
@@ -11574,17 +9508,6 @@
       <c r="H210" t="n">
         <v>0</v>
       </c>
-      <c r="I210" t="inlineStr"/>
-      <c r="J210" t="inlineStr"/>
-      <c r="K210" t="inlineStr"/>
-      <c r="L210" t="inlineStr"/>
-      <c r="M210" t="inlineStr"/>
-      <c r="N210" t="inlineStr"/>
-      <c r="O210" t="inlineStr"/>
-      <c r="P210" t="inlineStr"/>
-      <c r="Q210" t="inlineStr"/>
-      <c r="R210" t="inlineStr"/>
-      <c r="S210" t="inlineStr"/>
       <c r="T210" t="n">
         <v>0</v>
       </c>
@@ -11623,17 +9546,6 @@
       <c r="H211" t="n">
         <v>0</v>
       </c>
-      <c r="I211" t="inlineStr"/>
-      <c r="J211" t="inlineStr"/>
-      <c r="K211" t="inlineStr"/>
-      <c r="L211" t="inlineStr"/>
-      <c r="M211" t="inlineStr"/>
-      <c r="N211" t="inlineStr"/>
-      <c r="O211" t="inlineStr"/>
-      <c r="P211" t="inlineStr"/>
-      <c r="Q211" t="inlineStr"/>
-      <c r="R211" t="inlineStr"/>
-      <c r="S211" t="inlineStr"/>
       <c r="T211" t="n">
         <v>0</v>
       </c>
@@ -11672,17 +9584,6 @@
       <c r="H212" t="n">
         <v>0</v>
       </c>
-      <c r="I212" t="inlineStr"/>
-      <c r="J212" t="inlineStr"/>
-      <c r="K212" t="inlineStr"/>
-      <c r="L212" t="inlineStr"/>
-      <c r="M212" t="inlineStr"/>
-      <c r="N212" t="inlineStr"/>
-      <c r="O212" t="inlineStr"/>
-      <c r="P212" t="inlineStr"/>
-      <c r="Q212" t="inlineStr"/>
-      <c r="R212" t="inlineStr"/>
-      <c r="S212" t="inlineStr"/>
       <c r="T212" t="n">
         <v>0</v>
       </c>
@@ -11721,17 +9622,6 @@
       <c r="H213" t="n">
         <v>0</v>
       </c>
-      <c r="I213" t="inlineStr"/>
-      <c r="J213" t="inlineStr"/>
-      <c r="K213" t="inlineStr"/>
-      <c r="L213" t="inlineStr"/>
-      <c r="M213" t="inlineStr"/>
-      <c r="N213" t="inlineStr"/>
-      <c r="O213" t="inlineStr"/>
-      <c r="P213" t="inlineStr"/>
-      <c r="Q213" t="inlineStr"/>
-      <c r="R213" t="inlineStr"/>
-      <c r="S213" t="inlineStr"/>
       <c r="T213" t="n">
         <v>0</v>
       </c>
@@ -11770,17 +9660,6 @@
       <c r="H214" t="n">
         <v>0</v>
       </c>
-      <c r="I214" t="inlineStr"/>
-      <c r="J214" t="inlineStr"/>
-      <c r="K214" t="inlineStr"/>
-      <c r="L214" t="inlineStr"/>
-      <c r="M214" t="inlineStr"/>
-      <c r="N214" t="inlineStr"/>
-      <c r="O214" t="inlineStr"/>
-      <c r="P214" t="inlineStr"/>
-      <c r="Q214" t="inlineStr"/>
-      <c r="R214" t="inlineStr"/>
-      <c r="S214" t="inlineStr"/>
       <c r="T214" t="n">
         <v>0</v>
       </c>
@@ -11819,17 +9698,6 @@
       <c r="H215" t="n">
         <v>0</v>
       </c>
-      <c r="I215" t="inlineStr"/>
-      <c r="J215" t="inlineStr"/>
-      <c r="K215" t="inlineStr"/>
-      <c r="L215" t="inlineStr"/>
-      <c r="M215" t="inlineStr"/>
-      <c r="N215" t="inlineStr"/>
-      <c r="O215" t="inlineStr"/>
-      <c r="P215" t="inlineStr"/>
-      <c r="Q215" t="inlineStr"/>
-      <c r="R215" t="inlineStr"/>
-      <c r="S215" t="inlineStr"/>
       <c r="T215" t="n">
         <v>0</v>
       </c>
@@ -11868,17 +9736,6 @@
       <c r="H216" t="n">
         <v>0</v>
       </c>
-      <c r="I216" t="inlineStr"/>
-      <c r="J216" t="inlineStr"/>
-      <c r="K216" t="inlineStr"/>
-      <c r="L216" t="inlineStr"/>
-      <c r="M216" t="inlineStr"/>
-      <c r="N216" t="inlineStr"/>
-      <c r="O216" t="inlineStr"/>
-      <c r="P216" t="inlineStr"/>
-      <c r="Q216" t="inlineStr"/>
-      <c r="R216" t="inlineStr"/>
-      <c r="S216" t="inlineStr"/>
       <c r="T216" t="n">
         <v>0</v>
       </c>
@@ -11917,17 +9774,6 @@
       <c r="H217" t="n">
         <v>0</v>
       </c>
-      <c r="I217" t="inlineStr"/>
-      <c r="J217" t="inlineStr"/>
-      <c r="K217" t="inlineStr"/>
-      <c r="L217" t="inlineStr"/>
-      <c r="M217" t="inlineStr"/>
-      <c r="N217" t="inlineStr"/>
-      <c r="O217" t="inlineStr"/>
-      <c r="P217" t="inlineStr"/>
-      <c r="Q217" t="inlineStr"/>
-      <c r="R217" t="inlineStr"/>
-      <c r="S217" t="inlineStr"/>
       <c r="T217" t="n">
         <v>0</v>
       </c>
@@ -11966,17 +9812,6 @@
       <c r="H218" t="n">
         <v>0</v>
       </c>
-      <c r="I218" t="inlineStr"/>
-      <c r="J218" t="inlineStr"/>
-      <c r="K218" t="inlineStr"/>
-      <c r="L218" t="inlineStr"/>
-      <c r="M218" t="inlineStr"/>
-      <c r="N218" t="inlineStr"/>
-      <c r="O218" t="inlineStr"/>
-      <c r="P218" t="inlineStr"/>
-      <c r="Q218" t="inlineStr"/>
-      <c r="R218" t="inlineStr"/>
-      <c r="S218" t="inlineStr"/>
       <c r="T218" t="n">
         <v>0</v>
       </c>
@@ -12015,17 +9850,6 @@
       <c r="H219" t="n">
         <v>0</v>
       </c>
-      <c r="I219" t="inlineStr"/>
-      <c r="J219" t="inlineStr"/>
-      <c r="K219" t="inlineStr"/>
-      <c r="L219" t="inlineStr"/>
-      <c r="M219" t="inlineStr"/>
-      <c r="N219" t="inlineStr"/>
-      <c r="O219" t="inlineStr"/>
-      <c r="P219" t="inlineStr"/>
-      <c r="Q219" t="inlineStr"/>
-      <c r="R219" t="inlineStr"/>
-      <c r="S219" t="inlineStr"/>
       <c r="T219" t="n">
         <v>0</v>
       </c>
@@ -12064,17 +9888,6 @@
       <c r="H220" t="n">
         <v>0</v>
       </c>
-      <c r="I220" t="inlineStr"/>
-      <c r="J220" t="inlineStr"/>
-      <c r="K220" t="inlineStr"/>
-      <c r="L220" t="inlineStr"/>
-      <c r="M220" t="inlineStr"/>
-      <c r="N220" t="inlineStr"/>
-      <c r="O220" t="inlineStr"/>
-      <c r="P220" t="inlineStr"/>
-      <c r="Q220" t="inlineStr"/>
-      <c r="R220" t="inlineStr"/>
-      <c r="S220" t="inlineStr"/>
       <c r="T220" t="n">
         <v>0</v>
       </c>
@@ -12113,17 +9926,6 @@
       <c r="H221" t="n">
         <v>0</v>
       </c>
-      <c r="I221" t="inlineStr"/>
-      <c r="J221" t="inlineStr"/>
-      <c r="K221" t="inlineStr"/>
-      <c r="L221" t="inlineStr"/>
-      <c r="M221" t="inlineStr"/>
-      <c r="N221" t="inlineStr"/>
-      <c r="O221" t="inlineStr"/>
-      <c r="P221" t="inlineStr"/>
-      <c r="Q221" t="inlineStr"/>
-      <c r="R221" t="inlineStr"/>
-      <c r="S221" t="inlineStr"/>
       <c r="T221" t="n">
         <v>0</v>
       </c>
@@ -12162,17 +9964,6 @@
       <c r="H222" t="n">
         <v>0</v>
       </c>
-      <c r="I222" t="inlineStr"/>
-      <c r="J222" t="inlineStr"/>
-      <c r="K222" t="inlineStr"/>
-      <c r="L222" t="inlineStr"/>
-      <c r="M222" t="inlineStr"/>
-      <c r="N222" t="inlineStr"/>
-      <c r="O222" t="inlineStr"/>
-      <c r="P222" t="inlineStr"/>
-      <c r="Q222" t="inlineStr"/>
-      <c r="R222" t="inlineStr"/>
-      <c r="S222" t="inlineStr"/>
       <c r="T222" t="n">
         <v>0</v>
       </c>
@@ -12211,17 +10002,6 @@
       <c r="H223" t="n">
         <v>0</v>
       </c>
-      <c r="I223" t="inlineStr"/>
-      <c r="J223" t="inlineStr"/>
-      <c r="K223" t="inlineStr"/>
-      <c r="L223" t="inlineStr"/>
-      <c r="M223" t="inlineStr"/>
-      <c r="N223" t="inlineStr"/>
-      <c r="O223" t="inlineStr"/>
-      <c r="P223" t="inlineStr"/>
-      <c r="Q223" t="inlineStr"/>
-      <c r="R223" t="inlineStr"/>
-      <c r="S223" t="inlineStr"/>
       <c r="T223" t="n">
         <v>0</v>
       </c>
@@ -12260,17 +10040,6 @@
       <c r="H224" t="n">
         <v>0</v>
       </c>
-      <c r="I224" t="inlineStr"/>
-      <c r="J224" t="inlineStr"/>
-      <c r="K224" t="inlineStr"/>
-      <c r="L224" t="inlineStr"/>
-      <c r="M224" t="inlineStr"/>
-      <c r="N224" t="inlineStr"/>
-      <c r="O224" t="inlineStr"/>
-      <c r="P224" t="inlineStr"/>
-      <c r="Q224" t="inlineStr"/>
-      <c r="R224" t="inlineStr"/>
-      <c r="S224" t="inlineStr"/>
       <c r="T224" t="n">
         <v>0</v>
       </c>
@@ -12309,17 +10078,6 @@
       <c r="H225" t="n">
         <v>0</v>
       </c>
-      <c r="I225" t="inlineStr"/>
-      <c r="J225" t="inlineStr"/>
-      <c r="K225" t="inlineStr"/>
-      <c r="L225" t="inlineStr"/>
-      <c r="M225" t="inlineStr"/>
-      <c r="N225" t="inlineStr"/>
-      <c r="O225" t="inlineStr"/>
-      <c r="P225" t="inlineStr"/>
-      <c r="Q225" t="inlineStr"/>
-      <c r="R225" t="inlineStr"/>
-      <c r="S225" t="inlineStr"/>
       <c r="T225" t="n">
         <v>0</v>
       </c>
@@ -12358,17 +10116,6 @@
       <c r="H226" t="n">
         <v>0</v>
       </c>
-      <c r="I226" t="inlineStr"/>
-      <c r="J226" t="inlineStr"/>
-      <c r="K226" t="inlineStr"/>
-      <c r="L226" t="inlineStr"/>
-      <c r="M226" t="inlineStr"/>
-      <c r="N226" t="inlineStr"/>
-      <c r="O226" t="inlineStr"/>
-      <c r="P226" t="inlineStr"/>
-      <c r="Q226" t="inlineStr"/>
-      <c r="R226" t="inlineStr"/>
-      <c r="S226" t="inlineStr"/>
       <c r="T226" t="n">
         <v>0</v>
       </c>
@@ -12407,17 +10154,6 @@
       <c r="H227" t="n">
         <v>0</v>
       </c>
-      <c r="I227" t="inlineStr"/>
-      <c r="J227" t="inlineStr"/>
-      <c r="K227" t="inlineStr"/>
-      <c r="L227" t="inlineStr"/>
-      <c r="M227" t="inlineStr"/>
-      <c r="N227" t="inlineStr"/>
-      <c r="O227" t="inlineStr"/>
-      <c r="P227" t="inlineStr"/>
-      <c r="Q227" t="inlineStr"/>
-      <c r="R227" t="inlineStr"/>
-      <c r="S227" t="inlineStr"/>
       <c r="T227" t="n">
         <v>0</v>
       </c>
@@ -12456,17 +10192,6 @@
       <c r="H228" t="n">
         <v>0</v>
       </c>
-      <c r="I228" t="inlineStr"/>
-      <c r="J228" t="inlineStr"/>
-      <c r="K228" t="inlineStr"/>
-      <c r="L228" t="inlineStr"/>
-      <c r="M228" t="inlineStr"/>
-      <c r="N228" t="inlineStr"/>
-      <c r="O228" t="inlineStr"/>
-      <c r="P228" t="inlineStr"/>
-      <c r="Q228" t="inlineStr"/>
-      <c r="R228" t="inlineStr"/>
-      <c r="S228" t="inlineStr"/>
       <c r="T228" t="n">
         <v>0</v>
       </c>
@@ -12505,17 +10230,6 @@
       <c r="H229" t="n">
         <v>0</v>
       </c>
-      <c r="I229" t="inlineStr"/>
-      <c r="J229" t="inlineStr"/>
-      <c r="K229" t="inlineStr"/>
-      <c r="L229" t="inlineStr"/>
-      <c r="M229" t="inlineStr"/>
-      <c r="N229" t="inlineStr"/>
-      <c r="O229" t="inlineStr"/>
-      <c r="P229" t="inlineStr"/>
-      <c r="Q229" t="inlineStr"/>
-      <c r="R229" t="inlineStr"/>
-      <c r="S229" t="inlineStr"/>
       <c r="T229" t="n">
         <v>0</v>
       </c>
@@ -12554,17 +10268,6 @@
       <c r="H230" t="n">
         <v>0</v>
       </c>
-      <c r="I230" t="inlineStr"/>
-      <c r="J230" t="inlineStr"/>
-      <c r="K230" t="inlineStr"/>
-      <c r="L230" t="inlineStr"/>
-      <c r="M230" t="inlineStr"/>
-      <c r="N230" t="inlineStr"/>
-      <c r="O230" t="inlineStr"/>
-      <c r="P230" t="inlineStr"/>
-      <c r="Q230" t="inlineStr"/>
-      <c r="R230" t="inlineStr"/>
-      <c r="S230" t="inlineStr"/>
       <c r="T230" t="n">
         <v>0</v>
       </c>
@@ -12603,17 +10306,6 @@
       <c r="H231" t="n">
         <v>0</v>
       </c>
-      <c r="I231" t="inlineStr"/>
-      <c r="J231" t="inlineStr"/>
-      <c r="K231" t="inlineStr"/>
-      <c r="L231" t="inlineStr"/>
-      <c r="M231" t="inlineStr"/>
-      <c r="N231" t="inlineStr"/>
-      <c r="O231" t="inlineStr"/>
-      <c r="P231" t="inlineStr"/>
-      <c r="Q231" t="inlineStr"/>
-      <c r="R231" t="inlineStr"/>
-      <c r="S231" t="inlineStr"/>
       <c r="T231" t="n">
         <v>0</v>
       </c>
@@ -12652,17 +10344,6 @@
       <c r="H232" t="n">
         <v>0</v>
       </c>
-      <c r="I232" t="inlineStr"/>
-      <c r="J232" t="inlineStr"/>
-      <c r="K232" t="inlineStr"/>
-      <c r="L232" t="inlineStr"/>
-      <c r="M232" t="inlineStr"/>
-      <c r="N232" t="inlineStr"/>
-      <c r="O232" t="inlineStr"/>
-      <c r="P232" t="inlineStr"/>
-      <c r="Q232" t="inlineStr"/>
-      <c r="R232" t="inlineStr"/>
-      <c r="S232" t="inlineStr"/>
       <c r="T232" t="n">
         <v>0</v>
       </c>
@@ -12701,17 +10382,6 @@
       <c r="H233" t="n">
         <v>0</v>
       </c>
-      <c r="I233" t="inlineStr"/>
-      <c r="J233" t="inlineStr"/>
-      <c r="K233" t="inlineStr"/>
-      <c r="L233" t="inlineStr"/>
-      <c r="M233" t="inlineStr"/>
-      <c r="N233" t="inlineStr"/>
-      <c r="O233" t="inlineStr"/>
-      <c r="P233" t="inlineStr"/>
-      <c r="Q233" t="inlineStr"/>
-      <c r="R233" t="inlineStr"/>
-      <c r="S233" t="inlineStr"/>
       <c r="T233" t="n">
         <v>0</v>
       </c>
@@ -12750,17 +10420,6 @@
       <c r="H234" t="n">
         <v>0</v>
       </c>
-      <c r="I234" t="inlineStr"/>
-      <c r="J234" t="inlineStr"/>
-      <c r="K234" t="inlineStr"/>
-      <c r="L234" t="inlineStr"/>
-      <c r="M234" t="inlineStr"/>
-      <c r="N234" t="inlineStr"/>
-      <c r="O234" t="inlineStr"/>
-      <c r="P234" t="inlineStr"/>
-      <c r="Q234" t="inlineStr"/>
-      <c r="R234" t="inlineStr"/>
-      <c r="S234" t="inlineStr"/>
       <c r="T234" t="n">
         <v>0</v>
       </c>
@@ -12799,17 +10458,6 @@
       <c r="H235" t="n">
         <v>0</v>
       </c>
-      <c r="I235" t="inlineStr"/>
-      <c r="J235" t="inlineStr"/>
-      <c r="K235" t="inlineStr"/>
-      <c r="L235" t="inlineStr"/>
-      <c r="M235" t="inlineStr"/>
-      <c r="N235" t="inlineStr"/>
-      <c r="O235" t="inlineStr"/>
-      <c r="P235" t="inlineStr"/>
-      <c r="Q235" t="inlineStr"/>
-      <c r="R235" t="inlineStr"/>
-      <c r="S235" t="inlineStr"/>
       <c r="T235" t="n">
         <v>0</v>
       </c>
@@ -12848,17 +10496,6 @@
       <c r="H236" t="n">
         <v>0</v>
       </c>
-      <c r="I236" t="inlineStr"/>
-      <c r="J236" t="inlineStr"/>
-      <c r="K236" t="inlineStr"/>
-      <c r="L236" t="inlineStr"/>
-      <c r="M236" t="inlineStr"/>
-      <c r="N236" t="inlineStr"/>
-      <c r="O236" t="inlineStr"/>
-      <c r="P236" t="inlineStr"/>
-      <c r="Q236" t="inlineStr"/>
-      <c r="R236" t="inlineStr"/>
-      <c r="S236" t="inlineStr"/>
       <c r="T236" t="n">
         <v>0</v>
       </c>
@@ -12897,17 +10534,6 @@
       <c r="H237" t="n">
         <v>0</v>
       </c>
-      <c r="I237" t="inlineStr"/>
-      <c r="J237" t="inlineStr"/>
-      <c r="K237" t="inlineStr"/>
-      <c r="L237" t="inlineStr"/>
-      <c r="M237" t="inlineStr"/>
-      <c r="N237" t="inlineStr"/>
-      <c r="O237" t="inlineStr"/>
-      <c r="P237" t="inlineStr"/>
-      <c r="Q237" t="inlineStr"/>
-      <c r="R237" t="inlineStr"/>
-      <c r="S237" t="inlineStr"/>
       <c r="T237" t="n">
         <v>0</v>
       </c>
@@ -12946,17 +10572,6 @@
       <c r="H238" t="n">
         <v>0</v>
       </c>
-      <c r="I238" t="inlineStr"/>
-      <c r="J238" t="inlineStr"/>
-      <c r="K238" t="inlineStr"/>
-      <c r="L238" t="inlineStr"/>
-      <c r="M238" t="inlineStr"/>
-      <c r="N238" t="inlineStr"/>
-      <c r="O238" t="inlineStr"/>
-      <c r="P238" t="inlineStr"/>
-      <c r="Q238" t="inlineStr"/>
-      <c r="R238" t="inlineStr"/>
-      <c r="S238" t="inlineStr"/>
       <c r="T238" t="n">
         <v>0</v>
       </c>
@@ -12995,17 +10610,6 @@
       <c r="H239" t="n">
         <v>0</v>
       </c>
-      <c r="I239" t="inlineStr"/>
-      <c r="J239" t="inlineStr"/>
-      <c r="K239" t="inlineStr"/>
-      <c r="L239" t="inlineStr"/>
-      <c r="M239" t="inlineStr"/>
-      <c r="N239" t="inlineStr"/>
-      <c r="O239" t="inlineStr"/>
-      <c r="P239" t="inlineStr"/>
-      <c r="Q239" t="inlineStr"/>
-      <c r="R239" t="inlineStr"/>
-      <c r="S239" t="inlineStr"/>
       <c r="T239" t="n">
         <v>0</v>
       </c>
@@ -13044,17 +10648,6 @@
       <c r="H240" t="n">
         <v>0</v>
       </c>
-      <c r="I240" t="inlineStr"/>
-      <c r="J240" t="inlineStr"/>
-      <c r="K240" t="inlineStr"/>
-      <c r="L240" t="inlineStr"/>
-      <c r="M240" t="inlineStr"/>
-      <c r="N240" t="inlineStr"/>
-      <c r="O240" t="inlineStr"/>
-      <c r="P240" t="inlineStr"/>
-      <c r="Q240" t="inlineStr"/>
-      <c r="R240" t="inlineStr"/>
-      <c r="S240" t="inlineStr"/>
       <c r="T240" t="n">
         <v>0</v>
       </c>
@@ -13093,17 +10686,6 @@
       <c r="H241" t="n">
         <v>0</v>
       </c>
-      <c r="I241" t="inlineStr"/>
-      <c r="J241" t="inlineStr"/>
-      <c r="K241" t="inlineStr"/>
-      <c r="L241" t="inlineStr"/>
-      <c r="M241" t="inlineStr"/>
-      <c r="N241" t="inlineStr"/>
-      <c r="O241" t="inlineStr"/>
-      <c r="P241" t="inlineStr"/>
-      <c r="Q241" t="inlineStr"/>
-      <c r="R241" t="inlineStr"/>
-      <c r="S241" t="inlineStr"/>
       <c r="T241" t="n">
         <v>0</v>
       </c>
@@ -13142,17 +10724,6 @@
       <c r="H242" t="n">
         <v>0</v>
       </c>
-      <c r="I242" t="inlineStr"/>
-      <c r="J242" t="inlineStr"/>
-      <c r="K242" t="inlineStr"/>
-      <c r="L242" t="inlineStr"/>
-      <c r="M242" t="inlineStr"/>
-      <c r="N242" t="inlineStr"/>
-      <c r="O242" t="inlineStr"/>
-      <c r="P242" t="inlineStr"/>
-      <c r="Q242" t="inlineStr"/>
-      <c r="R242" t="inlineStr"/>
-      <c r="S242" t="inlineStr"/>
       <c r="T242" t="n">
         <v>0</v>
       </c>
@@ -13191,17 +10762,6 @@
       <c r="H243" t="n">
         <v>0</v>
       </c>
-      <c r="I243" t="inlineStr"/>
-      <c r="J243" t="inlineStr"/>
-      <c r="K243" t="inlineStr"/>
-      <c r="L243" t="inlineStr"/>
-      <c r="M243" t="inlineStr"/>
-      <c r="N243" t="inlineStr"/>
-      <c r="O243" t="inlineStr"/>
-      <c r="P243" t="inlineStr"/>
-      <c r="Q243" t="inlineStr"/>
-      <c r="R243" t="inlineStr"/>
-      <c r="S243" t="inlineStr"/>
       <c r="T243" t="n">
         <v>0</v>
       </c>
@@ -13240,17 +10800,6 @@
       <c r="H244" t="n">
         <v>0</v>
       </c>
-      <c r="I244" t="inlineStr"/>
-      <c r="J244" t="inlineStr"/>
-      <c r="K244" t="inlineStr"/>
-      <c r="L244" t="inlineStr"/>
-      <c r="M244" t="inlineStr"/>
-      <c r="N244" t="inlineStr"/>
-      <c r="O244" t="inlineStr"/>
-      <c r="P244" t="inlineStr"/>
-      <c r="Q244" t="inlineStr"/>
-      <c r="R244" t="inlineStr"/>
-      <c r="S244" t="inlineStr"/>
       <c r="T244" t="n">
         <v>0</v>
       </c>
@@ -15005,6 +12554,13 @@
           <t>DE;EE;FR;IT;LT;LV</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15022,6 +12578,13 @@
           <t>DE;FR;IT;LV;PL</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15039,6 +12602,13 @@
           <t>DE;FR;IT;LV</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15056,6 +12626,13 @@
           <t>DE;FR;IT</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15063,6 +12640,7 @@
           <t>VIG23</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>DE;FR</t>
@@ -15078,6 +12656,11 @@
           <t>DE;FR</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15085,6 +12668,7 @@
           <t>RST23</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>DE;FR;IT</t>
@@ -15095,6 +12679,12 @@
           <t>DE;FR;IT</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -15102,6 +12692,8 @@
           <t>MET23</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>DE;FR;PL</t>
@@ -15112,103 +12704,151 @@
           <t>DE;FR;PL</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VIG24</t>
-        </is>
-      </c>
+          <t>REC23</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AT;DE;ES;FR;PL</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AT;DE;ES;FR;PL</t>
-        </is>
-      </c>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AIF24</t>
-        </is>
-      </c>
+          <t>VIG24</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>DE;FR</t>
+          <t>AT;DE;ES;FR;PL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>DE;FR</t>
-        </is>
-      </c>
+          <t>AT;DE;ES;FR;PL</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AIF24-2</t>
+          <t>SNT24</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>DE</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>DE;FR;IT;PL</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>DE;FR;IT;PL</t>
-        </is>
-      </c>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SEK24</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>DE;FR;IT;LT;SK</t>
-        </is>
-      </c>
+          <t>SKY24</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>DE;FR;IT;LT;SK</t>
-        </is>
-      </c>
+          <t>DE;FR</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MET24</t>
+          <t>DFR24</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>DE;FR</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>DE;FR;PL</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>DE;FR;PL</t>
-        </is>
-      </c>
+          <t>DE;FR</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>OAI24</t>
+          <t>AIF24</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>DE;FR</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>DE;FR;IT;PL</t>
-        </is>
-      </c>
+          <t>DE;FR</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -15216,145 +12856,180 @@
           <t>EDM24</t>
         </is>
       </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>BG;CY;CZ;DK;EE;EL;FI;HR;HU;IE;IT;LT;LV;NL;PT;RO;SE;SI;SK</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CHK24</t>
-        </is>
-      </c>
+          <t>SEK24</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>DE;FR</t>
+          <t>DE;FR;IT;LT;SK</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>DE;FR</t>
-        </is>
-      </c>
+          <t>DE;FR;IT;LT;SK</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>VIG24-2</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>DE;FR;IT</t>
-        </is>
-      </c>
+          <t>AIF24-2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>DE;FR;IT</t>
+          <t>DE;FR;IT;PL</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>DE;FR;IT</t>
-        </is>
-      </c>
+          <t>DE;FR;IT;PL</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FFO24</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
+          <t>OAI24</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
+          <t>DE;FR;IT;PL</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>EAS24</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>DE;ES;FR;IT;PL</t>
-        </is>
-      </c>
+          <t>CHK24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>DE;ES;FR;IT;PL</t>
+          <t>DE;FR</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>DE;ES;FR;IT;PL</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>DE;ES;FR;IT;PL</t>
-        </is>
-      </c>
+          <t>DE;FR</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DFR24</t>
+          <t>FFO24</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>DE</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>DE;FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>DE;FR</t>
-        </is>
-      </c>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HFL24</t>
+          <t>VIG24-2</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>DE;FR;IT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>DE;FR;HU;PL</t>
+          <t>DE;FR;IT</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>DE;FR;HU;PL</t>
-        </is>
-      </c>
+          <t>DE;FR;IT</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BLV24-ENG</t>
-        </is>
-      </c>
+          <t>EAS24</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
           <t>DE;ES;FR;IT;PL</t>
@@ -15375,91 +13050,181 @@
           <t>DE;ES;FR;IT;PL</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SNT24</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
+          <t>HFL24</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>DE</t>
-        </is>
-      </c>
+          <t>DE;FR;HU;PL</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>DE;FR;HU;PL</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>REC23</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
+          <t>MET24</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>DE</t>
-        </is>
-      </c>
+          <t>DE;FR;PL</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>DE;FR;PL</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SKY24</t>
+          <t>BLV24-ENG</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>DE;ES;FR;IT;PL</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>DE;ES;FR;IT;PL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>DE;FR</t>
-        </is>
-      </c>
+          <t>DE;ES;FR;IT;PL</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>DE;ES;FR;IT;PL</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ISD25</t>
+          <t>CMS24</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>DE;FR;IT;PL</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>DE;FR;IT;PL</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
+          <t>DE;FR;IT;PL</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>REC25</t>
+          <t>MET24-2</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>DE;FR;IT;LV;PL</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>DE;FR;IT;LV;PL</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>DE;FR;IT;LV;PL</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>DE;FR;IT;LV;PL</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>DE;FR;IT;LV;PL</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>DE;FR;IT;LV;PL</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>DE</t>
-        </is>
-      </c>
+          <t>DE;FR;IT;LV;PL</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CMS24</t>
+          <t>CHK25</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>DE;FR;IT;PL</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>DE;FR;IT;PL</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>DE;FR;IT;PL</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -15477,6 +13242,9 @@
           <t>DE;FR;IT;PL</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -15484,107 +13252,91 @@
           <t>CMS25-ENG</t>
         </is>
       </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CHK25</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>DE;FR;IT;PL</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>DE;FR;IT;PL</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>DE;FR;IT;PL</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>DE;FR;IT;PL</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>DE;FR;IT;PL</t>
-        </is>
-      </c>
+          <t>MET25</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>DE;FR;IT;PL</t>
-        </is>
-      </c>
+          <t>DE;FR;PL</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>DE;FR;PL</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MET25</t>
-        </is>
-      </c>
+          <t>ISD25</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>DE;FR;PL</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>DE;FR;PL</t>
-        </is>
-      </c>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MET24-2</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>DE;FR;IT;LV;PL</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>DE;FR;IT;LV;PL</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>DE;FR;IT;LV;PL</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>DE;FR;IT;LV;PL</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>DE;FR;IT;LV;PL</t>
-        </is>
-      </c>
+          <t>REC25</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>DE;FR;IT;LV;PL</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>DE;FR;IT;LV;PL</t>
-        </is>
-      </c>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
